--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F893"/>
+  <dimension ref="A1:F913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>PRC-29.007/2017-B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Extinto</t>
+          <t>DC-008/2021</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-22.016/2020</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-22.016/2020</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-003/2021</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Registro de Preços</t>
+          <t>RP 245/2021</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -16812,7 +16812,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Rescindido</t>
+          <t>DC-010/2021</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -21820,7 +21820,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -21852,7 +21852,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
@@ -21884,7 +21884,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C722" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C723" t="inlineStr">
@@ -21948,7 +21948,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C724" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
@@ -22012,7 +22012,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -24972,7 +24972,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -25286,12 +25286,12 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25318,12 +25318,12 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25345,17 +25345,17 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25377,17 +25377,17 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -25409,17 +25409,17 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -25441,17 +25441,17 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -25463,26 +25463,46 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B845" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C845" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D845" t="inlineStr"/>
-      <c r="E845" t="inlineStr"/>
-      <c r="F845" t="inlineStr"/>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>-17.21201508102213</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B846" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C846" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25490,23 +25510,31 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
-        </is>
-      </c>
-      <c r="F846" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B847" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C847" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25514,25 +25542,29 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
-      <c r="F847" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25542,29 +25574,29 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25574,29 +25606,29 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25606,29 +25638,29 @@
       </c>
       <c r="D850" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E850" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -25636,23 +25668,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25660,58 +25700,66 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
-      <c r="E852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
-        </is>
-      </c>
-      <c r="B853" t="inlineStr"/>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>9501894</t>
+        </is>
+      </c>
       <c r="C853" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-21.1994491</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr"/>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B854" t="inlineStr"/>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>9518766</t>
+        </is>
+      </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-15.483562</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
+          <t>-44.39677500000001</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -25719,23 +25767,27 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B855" t="inlineStr"/>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>9518766</t>
+        </is>
+      </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-15.5007309</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
+          <t>-44.7624674</t>
         </is>
       </c>
       <c r="F855" t="inlineStr"/>
@@ -25743,10 +25795,14 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B856" t="inlineStr"/>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
       <c r="C856" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25754,23 +25810,31 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
-      <c r="F856" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
-        </is>
-      </c>
-      <c r="B857" t="inlineStr"/>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
       <c r="C857" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25778,49 +25842,61 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>-19.6107675</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>-42.64891799999999</t>
-        </is>
-      </c>
-      <c r="F857" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25828,31 +25904,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25864,19 +25932,19 @@
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25888,19 +25956,19 @@
       <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25908,31 +25976,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -25944,19 +26004,19 @@
       <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -25968,17 +26028,21 @@
       <c r="E864" t="inlineStr"/>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C865" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25986,15 +26050,23 @@
       </c>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr"/>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B866" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C866" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26002,15 +26074,23 @@
       </c>
       <c r="D866" t="inlineStr"/>
       <c r="E866" t="inlineStr"/>
-      <c r="F866" t="inlineStr"/>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr"/>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
       <c r="C867" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26018,12 +26098,12 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F867" t="inlineStr"/>
@@ -26031,92 +26111,96 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>-19.747173</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>1301606 000003/2025</t>
-        </is>
-      </c>
+          <t>-42.91331545001727</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr"/>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9515457</t>
+        </is>
+      </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>-21.23264738347681</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
       <c r="F869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-21.23528484003703</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
-      <c r="F870" t="inlineStr">
-        <is>
-          <t>2301901 000003/2021</t>
-        </is>
-      </c>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26124,55 +26208,51 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
-      <c r="F871" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-19.6107675</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-42.64891799999999</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr"/>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E872" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr"/>
+      <c r="E872" t="inlineStr"/>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26182,29 +26262,29 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-43.9495793253305</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26212,31 +26292,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E874" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26244,31 +26316,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E875" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -26276,23 +26340,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr"/>
-      <c r="E876" t="inlineStr"/>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -26304,115 +26376,79 @@
       <c r="E877" t="inlineStr"/>
       <c r="F877" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr"/>
       <c r="C879" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E879" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E880" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -26420,23 +26456,27 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>2301520 000036/2025</t>
-        </is>
-      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
@@ -26444,23 +26484,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D882" t="inlineStr"/>
-      <c r="E882" t="inlineStr"/>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26470,45 +26518,49 @@
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t>2301762 000026/2025</t>
-        </is>
-      </c>
+      <c r="F883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr"/>
-      <c r="E884" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26527,12 +26579,12 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26542,12 +26594,12 @@
       </c>
       <c r="D886" t="inlineStr">
         <is>
-          <t>-17.8518635</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E886" t="inlineStr">
         <is>
-          <t>-41.5076927</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
@@ -26559,12 +26611,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26574,91 +26626,143 @@
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>-20.6829764</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
         <is>
-          <t>-44.8232506</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B888" t="inlineStr"/>
+          <t>DC-9505062/2026</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>9505062</t>
+        </is>
+      </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Obra 4</t>
-        </is>
-      </c>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
-      <c r="F888" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>2301520 000044/2025</t>
+        </is>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B889" t="inlineStr"/>
+          <t>DM-9504058/2026</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>9504058</t>
+        </is>
+      </c>
       <c r="C889" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>2301762 000030/2025</t>
+        </is>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B890" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr"/>
-      <c r="F890" t="inlineStr"/>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B891" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D891" t="inlineStr"/>
       <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr"/>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
-      <c r="B892" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C892" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26666,31 +26770,539 @@
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr"/>
-      <c r="F892" t="inlineStr"/>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr"/>
+      <c r="E893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr"/>
+      <c r="E894" t="inlineStr"/>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr"/>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr"/>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>2301520 000036/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>9422079</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr"/>
+      <c r="E902" t="inlineStr"/>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr"/>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>9424304</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr"/>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr"/>
+      <c r="E909" t="inlineStr"/>
+      <c r="F909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr"/>
+      <c r="E910" t="inlineStr"/>
+      <c r="F910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr"/>
+      <c r="E912" t="inlineStr"/>
+      <c r="F912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B893" t="inlineStr"/>
-      <c r="C893" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D893" t="inlineStr">
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
         <is>
           <t>-18.46005275010656</t>
         </is>
       </c>
-      <c r="E893" t="inlineStr">
+      <c r="E913" t="inlineStr">
         <is>
           <t>-48.18218127247928</t>
         </is>
       </c>
-      <c r="F893" t="inlineStr"/>
+      <c r="F913" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F913"/>
+  <dimension ref="A1:F895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19711,12 +19711,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>9473911/2024</t>
+          <t>AMA-9461425/2025</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>9473911</t>
+          <t>9461425</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -19728,7 +19728,7 @@
       <c r="E645" t="inlineStr"/>
       <c r="F645" t="inlineStr">
         <is>
-          <t>1301017 000043/2024</t>
+          <t>2301617 000002/2025</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D646" t="inlineStr"/>
@@ -19759,36 +19759,44 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>AMA-9461425/2025</t>
+          <t>DM-9440653/2024</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>9461425</t>
+          <t>9440653</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D647" t="inlineStr"/>
-      <c r="E647" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-18.2398134</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-43.6049294</t>
+        </is>
+      </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>2301617 000002/2025</t>
+          <t>2301762 000008/2024</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>DM-9440653/2024</t>
+          <t>DM-9440655/2024</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>9440653</t>
+          <t>9440655</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -19798,12 +19806,12 @@
       </c>
       <c r="D648" t="inlineStr">
         <is>
-          <t>-18.2398134</t>
+          <t>-21.5799309</t>
         </is>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>-43.6049294</t>
+          <t>-45.4427049</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
@@ -19815,12 +19823,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>DM-9440655/2024</t>
+          <t>DM-9440649/2024</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>9440655</t>
+          <t>9440649</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -19830,12 +19838,12 @@
       </c>
       <c r="D649" t="inlineStr">
         <is>
-          <t>-21.5799309</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>-45.4427049</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
@@ -19847,12 +19855,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>DM-9440649/2024</t>
+          <t>DM-9440647/2024</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>9440649</t>
+          <t>9440647</t>
         </is>
       </c>
       <c r="C650" t="inlineStr">
@@ -19879,12 +19887,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>DM-9440647/2024</t>
+          <t>DM-9440658/2024</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>9440647</t>
+          <t>9440658</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -19894,12 +19902,12 @@
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-21.7876304</t>
         </is>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-46.5421144</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
@@ -19911,12 +19919,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>DM-9440658/2024</t>
+          <t>DM-9440661/2024</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>9440658</t>
+          <t>9440661</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -19926,12 +19934,12 @@
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>-21.7876304</t>
+          <t>-22.4315443</t>
         </is>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>-46.5421144</t>
+          <t>-45.4632342</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
@@ -19943,12 +19951,12 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>DM-9440661/2024</t>
+          <t>9439923</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>9440661</t>
+          <t>9439923</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -19958,29 +19966,29 @@
       </c>
       <c r="D653" t="inlineStr">
         <is>
-          <t>-22.4315443</t>
+          <t>-19.5952902</t>
         </is>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>-45.4632342</t>
+          <t>-46.9326049</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>2301762 000008/2024</t>
+          <t>2301707 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>9439923</t>
+          <t>DC-9447109/2024</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>9439923</t>
+          <t>9447109</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -19990,17 +19998,17 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-19.5952902</t>
+          <t>-14.757046772025067</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>-46.9326049</t>
+          <t>-43.93015192008537</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>2301707 000004/2024</t>
+          <t>2301520 000021/2024</t>
         </is>
       </c>
     </row>
@@ -20022,12 +20030,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-14.757046772025067</t>
+          <t>-19.783357402903007</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>-43.93015192008537</t>
+          <t>-43.951944370919506</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -20039,12 +20047,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>DC-9447109/2024</t>
+          <t>DC-9445587/2024</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>9447109</t>
+          <t>9445587</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -20054,17 +20062,17 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-19.783357402903007</t>
+          <t>-20.63168865721149</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>-43.951944370919506</t>
+          <t>-47.10193369380541</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>2301520 000021/2024</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
@@ -20086,12 +20094,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>-20.63168865721149</t>
+          <t>-20.6041089</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>-47.10193369380541</t>
+          <t>-46.9106488</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -20103,12 +20111,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>DC-9445587/2024</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>9445587</t>
+          <t>9472752</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20118,17 +20126,17 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>-20.6041089</t>
+          <t>-20.05185754871156</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>-46.9106488</t>
+          <t>-44.18814551429173</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301520 000008/2025</t>
         </is>
       </c>
     </row>
@@ -20150,12 +20158,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>-20.05185754871156</t>
+          <t>-20.130347305381726</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>-44.18814551429173</t>
+          <t>-44.19984053737846</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -20177,17 +20185,17 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>-20.130347305381726</t>
+          <t>-20.042186156631548</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>-44.19984053737846</t>
+          <t>-44.198824969508905</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -20214,12 +20222,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>-20.042186156631548</t>
+          <t>-20.009247062372893</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>-44.198824969508905</t>
+          <t>-44.204977569705186</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
@@ -20231,44 +20239,36 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>9472752</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D662" t="inlineStr">
-        <is>
-          <t>-20.009247062372893</t>
-        </is>
-      </c>
-      <c r="E662" t="inlineStr">
-        <is>
-          <t>-44.204977569705186</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr"/>
+      <c r="E662" t="inlineStr"/>
       <c r="F662" t="inlineStr">
         <is>
-          <t>2301520 000008/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DC-006/2024</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9422285</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -20276,23 +20276,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr"/>
-      <c r="E663" t="inlineStr"/>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-17.0321536895841</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>-46.014676019311956</t>
+        </is>
+      </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000016/2023</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>DC-006/2024</t>
+          <t>DM-007/2024</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>9422285</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -20300,31 +20308,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
-        <is>
-          <t>-17.0321536895841</t>
-        </is>
-      </c>
-      <c r="E664" t="inlineStr">
-        <is>
-          <t>-46.014676019311956</t>
-        </is>
-      </c>
+      <c r="D664" t="inlineStr"/>
+      <c r="E664" t="inlineStr"/>
       <c r="F664" t="inlineStr">
         <is>
-          <t>2301520 000016/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>DM-007/2024</t>
+          <t>DM-9437231</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9437231</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -20336,19 +20336,19 @@
       <c r="E665" t="inlineStr"/>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000006/2024</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>DM-9437231</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -20360,19 +20360,19 @@
       <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301403 000099/2024</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>9442805</t>
+          <t>DPEI-9447985</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>9442805</t>
+          <t>9447985</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -20380,23 +20380,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-19.9149659</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-43.9000041</t>
+        </is>
+      </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2301403 000099/2024</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>DPEI-9447985</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>9447985</t>
+          <t>9452477</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -20404,31 +20412,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr">
-        <is>
-          <t>-19.9149659</t>
-        </is>
-      </c>
-      <c r="E668" t="inlineStr">
-        <is>
-          <t>-43.9000041</t>
-        </is>
-      </c>
+      <c r="D668" t="inlineStr"/>
+      <c r="E668" t="inlineStr"/>
       <c r="F668" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301762 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>9452477</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20440,19 +20440,19 @@
       <c r="E669" t="inlineStr"/>
       <c r="F669" t="inlineStr">
         <is>
-          <t>2301762 000019/2024</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>DER-30.014/2025</t>
+          <t>DM-002/2024-B</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>DER-30.014/2025</t>
+          <t>9410208</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20460,23 +20460,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-19.638615</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-43.228648</t>
+        </is>
+      </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>DM-002/2024-B</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>9410208</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20486,29 +20494,29 @@
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>-19.638615</t>
+          <t>-15.97197985837174</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>-43.228648</t>
+          <t>-44.90024660668323</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DOV-002/2021-A</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -20516,31 +20524,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr">
-        <is>
-          <t>-15.97197985837174</t>
-        </is>
-      </c>
-      <c r="E672" t="inlineStr">
-        <is>
-          <t>-44.90024660668323</t>
-        </is>
-      </c>
+      <c r="D672" t="inlineStr"/>
+      <c r="E672" t="inlineStr"/>
       <c r="F672" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>DOV-002/2021-A</t>
+          <t>DM-026/2023-A</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>9292040</t>
+          <t>9407068</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -20552,19 +20552,19 @@
       <c r="E673" t="inlineStr"/>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>DM-026/2023-A</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>9407068</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -20583,12 +20583,12 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DOV-002/2022-B</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9344727</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -20600,19 +20600,19 @@
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>DOV-002/2022-B</t>
+          <t>DM-030/2023-B</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>9344727</t>
+          <t>9408491</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -20620,23 +20620,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-19.5068923</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-42.6044222</t>
+        </is>
+      </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>DM-030/2023-B</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>9408491</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -20646,17 +20654,17 @@
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>-19.5068923</t>
+          <t>-20.4799694</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>-42.6044222</t>
+          <t>-45.79996939999999</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
     </row>
@@ -20678,12 +20686,12 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>-20.4799694</t>
+          <t>-20.759954</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>-45.79996939999999</t>
+          <t>-45.918453</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
@@ -20695,12 +20703,12 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DM-025/2023-B</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9408445</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -20710,29 +20718,29 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>-20.759954</t>
+          <t>-16.8555088</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>-45.918453</t>
+          <t>-42.0630933</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>DM-025/2023-B</t>
+          <t>DOV-003/2022-B</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>9408445</t>
+          <t>9344739</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -20742,29 +20750,29 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>-16.8555088</t>
+          <t>-18.5967086</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>-42.0630933</t>
+          <t>-46.5181047</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>DOV-003/2022-B</t>
+          <t>DM-029/2023-B</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>9344739</t>
+          <t>9408476</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -20774,29 +20782,29 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>-18.5967086</t>
+          <t>-17.701729</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>-46.5181047</t>
+          <t>-42.515515</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>DM-029/2023-B</t>
+          <t>DM-026/2023-B</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>9408476</t>
+          <t>9407068</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -20806,12 +20814,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>-17.701729</t>
+          <t>-16.00026</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>-42.515515</t>
+          <t>-41.279238</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
@@ -20823,32 +20831,24 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>DM-026/2023-B</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>9407068</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D683" t="inlineStr">
-        <is>
-          <t>-16.00026</t>
-        </is>
-      </c>
-      <c r="E683" t="inlineStr">
-        <is>
-          <t>-41.279238</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr"/>
+      <c r="E683" t="inlineStr"/>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D684" t="inlineStr"/>
@@ -20879,12 +20879,12 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DC-005/2024</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9422256</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
@@ -20892,11 +20892,19 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr"/>
-      <c r="E685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-19.58691270347314</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-47.0726885458534</t>
+        </is>
+      </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000025/2023</t>
         </is>
       </c>
     </row>
@@ -20918,12 +20926,12 @@
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>-19.58691270347314</t>
+          <t>-19.528005598761357</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>-47.0726885458534</t>
+          <t>-47.07955421284039</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
@@ -20935,12 +20943,12 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>DC-005/2024</t>
+          <t>DOV-002/2022-A</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>9422256</t>
+          <t>9344727</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -20948,31 +20956,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr">
-        <is>
-          <t>-19.528005598761357</t>
-        </is>
-      </c>
-      <c r="E687" t="inlineStr">
-        <is>
-          <t>-47.07955421284039</t>
-        </is>
-      </c>
+      <c r="D687" t="inlineStr"/>
+      <c r="E687" t="inlineStr"/>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2301520 000025/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>DOV-002/2022-A</t>
+          <t>AMA-9445113/2024</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>9344727</t>
+          <t>9445113</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -20984,19 +20984,19 @@
       <c r="E688" t="inlineStr"/>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301617 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>AMA-9445113/2024</t>
+          <t>DM-001/2024-A</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>9445113</t>
+          <t>9410177</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -21008,19 +21008,19 @@
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2301617 000001/2024</t>
+          <t>2301762 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DM-001/2024-A</t>
+          <t>PRC-29.008/2017-D</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>9410177</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -21028,23 +21028,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2301762 000001/2024</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-D</t>
+          <t>DM-9445781/2024</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9445781</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -21052,31 +21060,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D691" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E691" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D691" t="inlineStr"/>
+      <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000015/2024</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>DM-9445781/2024</t>
+          <t>DM-9445821/2024</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>9445781</t>
+          <t>9445821</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -21088,19 +21088,19 @@
       <c r="E692" t="inlineStr"/>
       <c r="F692" t="inlineStr">
         <is>
-          <t>2301762 000015/2024</t>
+          <t>2301762 000012/2024</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DM-9445821/2024</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>9445821</t>
+          <t>9447456</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -21112,19 +21112,19 @@
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2301762 000012/2024</t>
+          <t>2301762 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DOV-004/2022-B</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>9447456</t>
+          <t>9344750</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -21136,19 +21136,19 @@
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2301762 000017/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DOV-004/2022-B</t>
+          <t>DM-028/2023-A</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>9344750</t>
+          <t>9408646</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -21160,19 +21160,19 @@
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>DM-028/2023-A</t>
+          <t>DPEI-9446143</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>9408646</t>
+          <t>9446143</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -21184,19 +21184,19 @@
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DPEI-9446143</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>9446143</t>
+          <t>9474704</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -21208,19 +21208,19 @@
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301762 000005/2025</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-002/2024-A</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>9474704</t>
+          <t>9410208</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -21232,19 +21232,19 @@
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
-          <t>2301762 000005/2025</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DM-002/2024-A</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>9410208</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -21256,19 +21256,19 @@
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -21280,19 +21280,19 @@
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -21304,19 +21304,19 @@
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DM-001/2024-B</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9410177</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -21328,19 +21328,19 @@
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301762 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>9447045/2024-A</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>9447045</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -21350,105 +21350,89 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-18.9494754</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.9593239</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>1301017 000012/2024</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DM-001/2024-B</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>9410177</t>
+          <t>9393459</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr">
         <is>
-          <t>2301762 000001/2024</t>
+          <t>2301601 000017/2022</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9393459</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D705" t="inlineStr">
-        <is>
-          <t>-18.9494754</t>
-        </is>
-      </c>
-      <c r="E705" t="inlineStr">
-        <is>
-          <t>-46.9593239</t>
-        </is>
-      </c>
+          <t>Obra 5</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301601 000017/2022</t>
         </is>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>9447043/2024-A</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>9447043</t>
+          <t>9393459</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D706" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr"/>
+      <c r="E706" t="inlineStr"/>
       <c r="F706" t="inlineStr">
         <is>
-          <t>1301017 000012/2024</t>
+          <t>2301601 000017/2022</t>
         </is>
       </c>
     </row>
@@ -21465,7 +21449,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D707" t="inlineStr"/>
@@ -21489,7 +21473,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Obra 5</t>
+          <t>Obra 6</t>
         </is>
       </c>
       <c r="D708" t="inlineStr"/>
@@ -21513,7 +21497,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D709" t="inlineStr"/>
@@ -21527,60 +21511,76 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9393459</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-16.1257215</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-45.7410578</t>
+        </is>
+      </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>2301601 000017/2022</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9393459</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>Obra 6</t>
-        </is>
-      </c>
-      <c r="D711" t="inlineStr"/>
-      <c r="E711" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-16.056339</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-45.14616599999999</t>
+        </is>
+      </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>2301601 000017/2022</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9393459</t>
+          <t>9417858</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -21588,23 +21588,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D712" t="inlineStr"/>
-      <c r="E712" t="inlineStr"/>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-16.1257215</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-45.7410578</t>
+        </is>
+      </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>2301601 000017/2022</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9417858</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -21614,12 +21622,12 @@
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>-16.1257215</t>
+          <t>-16.056339</t>
         </is>
       </c>
       <c r="E713" t="inlineStr">
         <is>
-          <t>-45.7410578</t>
+          <t>-45.14616599999999</t>
         </is>
       </c>
       <c r="F713" t="inlineStr">
@@ -21631,12 +21639,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DPEI-002/2024</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9414453</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -21646,29 +21654,29 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>-16.056339</t>
+          <t>-16.7204079</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>-45.14616599999999</t>
+          <t>-43.8540743</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DPEI-006/2024</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9417858</t>
+          <t>9416621</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -21678,29 +21686,29 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>-16.1257215</t>
+          <t>-21.5799309</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>-45.7410578</t>
+          <t>-45.4427049</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DPEI-007/2024</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9417858</t>
+          <t>9417534</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -21708,31 +21716,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr">
-        <is>
-          <t>-16.056339</t>
-        </is>
-      </c>
-      <c r="E716" t="inlineStr">
-        <is>
-          <t>-45.14616599999999</t>
-        </is>
-      </c>
+      <c r="D716" t="inlineStr"/>
+      <c r="E716" t="inlineStr"/>
       <c r="F716" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000006/2023</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DPEI-002/2024</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>9414453</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -21742,29 +21742,29 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>-16.7204079</t>
+          <t>-21.8657357</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>-43.8540743</t>
+          <t>-43.01008239999999</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DPEI-006/2024</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>9416621</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -21774,41 +21774,49 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>-21.5799309</t>
+          <t>-21.990801252388714</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>-45.4427049</t>
+          <t>-42.90995722615383</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>DPEI-007/2024</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>9417534</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>-21.36383967660115</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>-42.67405889386136</t>
+        </is>
+      </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>2301601 000006/2023</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
@@ -21825,17 +21833,17 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>-21.8657357</t>
+          <t>-21.36590506590777</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>-43.01008239999999</t>
+          <t>-42.474979263671926</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
@@ -21857,17 +21865,17 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>-21.990801252388714</t>
+          <t>-21.416023487875883</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>-42.90995722615383</t>
+          <t>-42.815412025192636</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
@@ -21889,17 +21897,17 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>-21.36383967660115</t>
+          <t>-21.457172674928085</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>-42.67405889386136</t>
+          <t>-42.966439771920605</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
@@ -21921,17 +21929,17 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>-21.36590506590777</t>
+          <t>-21.196157236212304</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>-42.474979263671926</t>
+          <t>-42.62543945670461</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -21953,17 +21961,17 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>-21.416023487875883</t>
+          <t>-21.151982349638054</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>-42.815412025192636</t>
+          <t>-42.79328856036735</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -21975,108 +21983,108 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DPEI-005/2024</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>9414322</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>-21.457172674928085</t>
+          <t>-19.776208</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>-42.966439771920605</t>
+          <t>-43.948441</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DPEI-004/2024</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>9416600</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>-21.196157236212304</t>
+          <t>-20.7561451</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>-42.62543945670461</t>
+          <t>-42.8800278</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DM-011/2024</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>-21.151982349638054</t>
+          <t>-17.335013</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>-42.79328856036735</t>
+          <t>-44.943418</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DPEI-005/2024</t>
+          <t>DPEI-003/2024</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>9414322</t>
+          <t>9417600</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -22086,12 +22094,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>-19.776208</t>
+          <t>-17.8517815</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>-43.948441</t>
+          <t>-41.5076261</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
@@ -22103,12 +22111,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DPEI-004/2024</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>9416600</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -22116,31 +22124,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>-20.7561451</t>
-        </is>
-      </c>
-      <c r="E729" t="inlineStr">
-        <is>
-          <t>-42.8800278</t>
-        </is>
-      </c>
+      <c r="D729" t="inlineStr"/>
+      <c r="E729" t="inlineStr"/>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DM-011/2024</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -22148,31 +22148,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E730" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D730" t="inlineStr"/>
+      <c r="E730" t="inlineStr"/>
       <c r="F730" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DPEI-003/2024</t>
+          <t>DC-008/2024</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>9417600</t>
+          <t>9428115</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -22182,29 +22174,29 @@
       </c>
       <c r="D731" t="inlineStr">
         <is>
-          <t>-17.8517815</t>
+          <t>-18.5985001</t>
         </is>
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>-41.5076261</t>
+          <t>-45.35339499999999</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301520 000012/2023</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DC-008/2024</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9428115</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -22212,23 +22204,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-18.43838275042916</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-45.07210155240797</t>
+        </is>
+      </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000012/2023</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DM-9445782/2024</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9445782</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -22236,23 +22236,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-22.4212558</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-45.47013339999999</t>
+        </is>
+      </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000114/2024</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DC-008/2024</t>
+          <t>DM-9445784/2024</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>9428115</t>
+          <t>9445784</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -22262,29 +22270,29 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>-18.5985001</t>
+          <t>-22.431496</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>-45.35339499999999</t>
+          <t>-45.4633029</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>2301520 000012/2023</t>
+          <t>2301762 000113/2024</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DC-008/2024</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9428115</t>
+          <t>9444079</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -22292,63 +22300,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr">
-        <is>
-          <t>-18.43838275042916</t>
-        </is>
-      </c>
-      <c r="E735" t="inlineStr">
-        <is>
-          <t>-45.07210155240797</t>
-        </is>
-      </c>
+      <c r="D735" t="inlineStr"/>
+      <c r="E735" t="inlineStr"/>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2301520 000012/2023</t>
+          <t>2301403 000100/2024</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DM-9445782/2024</t>
+          <t>DC-9444080/2024</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9445782</t>
+          <t>9444080</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>-22.4212558</t>
+          <t>-15.97197985837177</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>-45.47013339999999</t>
+          <t>-44.90024660668347</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>2301762 000114/2024</t>
+          <t>2301520 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DM-9445784/2024</t>
+          <t>DC-9444080/2024</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9445784</t>
+          <t>9444080</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -22358,29 +22358,29 @@
       </c>
       <c r="D737" t="inlineStr">
         <is>
-          <t>-22.431496</t>
+          <t>-15.9662564146642</t>
         </is>
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>-45.4633029</t>
+          <t>-44.90120778993473</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2301762 000113/2024</t>
+          <t>2301520 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DF/GTIC-9444079</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9444079</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
@@ -22388,55 +22388,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D738" t="inlineStr"/>
-      <c r="E738" t="inlineStr"/>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-19.8162654081741</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-43.9479415297562</t>
+        </is>
+      </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2301403 000100/2024</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DC-9444080/2024</t>
+          <t>DOV-004/2022-A</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9444080</t>
+          <t>9344750</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D739" t="inlineStr">
-        <is>
-          <t>-15.97197985837177</t>
-        </is>
-      </c>
-      <c r="E739" t="inlineStr">
-        <is>
-          <t>-44.90024660668347</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr"/>
+      <c r="E739" t="inlineStr"/>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2301520 000017/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DC-9444080/2024</t>
+          <t>DC-9439921/2024</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9444080</t>
+          <t>9439921</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -22446,29 +22446,29 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-15.9662564146642</t>
+          <t>-22.60722055771159</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>-44.90120778993473</t>
+          <t>-46.04116272282801</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>2301520 000017/2024</t>
+          <t>1301606 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DC-9439921/2024</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9439921</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -22478,29 +22478,29 @@
       </c>
       <c r="D741" t="inlineStr">
         <is>
-          <t>-19.8162654081741</t>
+          <t>-22.58244462625664</t>
         </is>
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>-43.9479415297562</t>
+          <t>-46.01200384097238</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>1301606 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DOV-004/2022-A</t>
+          <t>DM-029/2023-A</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9344750</t>
+          <t>9408476</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -22512,19 +22512,19 @@
       <c r="E742" t="inlineStr"/>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DC-9439921/2024</t>
+          <t>DM-030/2023-A</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>9439921</t>
+          <t>9408491</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -22534,29 +22534,29 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>-22.60722055771159</t>
+          <t>-19.5068923</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>-46.04116272282801</t>
+          <t>-42.6044222</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>1301606 000001/2024</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>DC-9439921/2024</t>
+          <t>DC-9445592/2024</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>9439921</t>
+          <t>9445592</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -22566,29 +22566,29 @@
       </c>
       <c r="D744" t="inlineStr">
         <is>
-          <t>-22.58244462625664</t>
+          <t>-19.716466</t>
         </is>
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>-46.01200384097238</t>
+          <t>-50.19527650000001</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>1301606 000001/2024</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>DM-029/2023-A</t>
+          <t>AEST-009440673/2024</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9408476</t>
+          <t>9440673</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -22600,19 +22600,19 @@
       <c r="E745" t="inlineStr"/>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301931 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DM-030/2023-A</t>
+          <t>DM-22.010/2019-E</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9408491</t>
+          <t>9241241</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -22622,29 +22622,29 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>-19.5068923</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>-42.6044222</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301762 000019/2019</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DC-9445592/2024</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9445592</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -22654,29 +22654,29 @@
       </c>
       <c r="D747" t="inlineStr">
         <is>
-          <t>-19.716466</t>
+          <t>-19.41249960000027</t>
         </is>
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>-50.19527650000001</t>
+          <t>-44.20754999999095</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>AEST-009440673/2024</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>9440673</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -22684,23 +22684,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-19.4067426</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-44.2266016</t>
+        </is>
+      </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>2301931 000001/2024</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-E</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>9241241</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="C749" t="inlineStr">
@@ -22710,61 +22718,61 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.4073712</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-44.20911359999999</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2301762 000019/2019</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
     </row>
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>-19.41249960000027</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>-44.20754999999095</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -22774,29 +22782,29 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>-19.4067426</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>-44.2266016</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
@@ -22804,63 +22812,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr">
-        <is>
-          <t>-19.4073712</t>
-        </is>
-      </c>
-      <c r="E752" t="inlineStr">
-        <is>
-          <t>-44.20911359999999</t>
-        </is>
-      </c>
+      <c r="D752" t="inlineStr"/>
+      <c r="E752" t="inlineStr"/>
       <c r="F752" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D753" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E753" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr"/>
+      <c r="E753" t="inlineStr"/>
       <c r="F753" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -22868,31 +22860,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D754" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E754" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D754" t="inlineStr"/>
+      <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -22904,19 +22888,19 @@
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -22928,19 +22912,19 @@
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9478759</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -22952,19 +22936,19 @@
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000029/2025</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9447761</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -22972,23 +22956,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr"/>
-      <c r="E758" t="inlineStr"/>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-21.78317377768046</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-45.83339382368384</t>
+        </is>
+      </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -22996,23 +22988,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr"/>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-21.7907786</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-45.7160543</t>
+        </is>
+      </c>
       <c r="F759" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>9478759</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -23024,19 +23024,19 @@
       <c r="E760" t="inlineStr"/>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2301520 000029/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>9447761</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -23044,31 +23044,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr">
-        <is>
-          <t>-21.78317377768046</t>
-        </is>
-      </c>
-      <c r="E761" t="inlineStr">
-        <is>
-          <t>-45.83339382368384</t>
-        </is>
-      </c>
+      <c r="D761" t="inlineStr"/>
+      <c r="E761" t="inlineStr"/>
       <c r="F761" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9472756/2025</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9472756</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -23076,31 +23068,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D762" t="inlineStr">
-        <is>
-          <t>-21.7907786</t>
-        </is>
-      </c>
-      <c r="E762" t="inlineStr">
-        <is>
-          <t>-45.7160543</t>
-        </is>
-      </c>
+      <c r="D762" t="inlineStr"/>
+      <c r="E762" t="inlineStr"/>
       <c r="F762" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301520 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -23108,25 +23092,29 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>-20.32294571170053</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>-42.67292083028444</t>
+        </is>
+      </c>
       <c r="F763" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr">
-        <is>
-          <t>9471879</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr"/>
       <c r="C764" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23134,21 +23122,17 @@
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr">
-        <is>
-          <t>2301762 000001/2025</t>
-        </is>
-      </c>
+      <c r="F764" t="inlineStr"/>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>9472756</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -23156,53 +23140,57 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>-14.77197791029356</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>-43.93723839761794</t>
+        </is>
+      </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>2301520 000002/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D766" t="inlineStr">
-        <is>
-          <t>-20.32294571170053</t>
-        </is>
-      </c>
-      <c r="E766" t="inlineStr">
-        <is>
-          <t>-42.67292083028444</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr"/>
+      <c r="E766" t="inlineStr"/>
       <c r="F766" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
-        </is>
-      </c>
-      <c r="B767" t="inlineStr"/>
+          <t>AMA-9447965/2025</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>9447965</t>
+        </is>
+      </c>
       <c r="C767" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23210,17 +23198,21 @@
       </c>
       <c r="D767" t="inlineStr"/>
       <c r="E767" t="inlineStr"/>
-      <c r="F767" t="inlineStr"/>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2301617 000004/2024</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9470151</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -23228,55 +23220,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D768" t="inlineStr">
-        <is>
-          <t>-14.77197791029356</t>
-        </is>
-      </c>
-      <c r="E768" t="inlineStr">
-        <is>
-          <t>-43.93723839761794</t>
-        </is>
-      </c>
+      <c r="D768" t="inlineStr"/>
+      <c r="E768" t="inlineStr"/>
       <c r="F768" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301601 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-9439838/2024</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9439838</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>-19.878035358432</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>-46.01755299600972</t>
+        </is>
+      </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301520 000011/2024</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>AMA-9447965/2025</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>9447965</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -23284,23 +23276,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D770" t="inlineStr"/>
-      <c r="E770" t="inlineStr"/>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>-19.78342141078643</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>-43.951935887975836</t>
+        </is>
+      </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>2301617 000004/2024</t>
+          <t>2301520 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DPEI-9447050</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>9470151</t>
+          <t>9447050</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -23312,19 +23312,19 @@
       <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr">
         <is>
-          <t>2301601 000003/2025</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>DC-9439838/2024</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>9439838</t>
+          <t>9468321</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -23334,29 +23334,29 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>-19.878035358432</t>
+          <t>-21.822481</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>-46.01755299600972</t>
+          <t>-43.319474</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>2301520 000011/2024</t>
+          <t>2301520 000007/2025</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -23366,29 +23366,29 @@
       </c>
       <c r="D773" t="inlineStr">
         <is>
-          <t>-19.78342141078643</t>
+          <t>-19.8898481</t>
         </is>
       </c>
       <c r="E773" t="inlineStr">
         <is>
-          <t>-43.951935887975836</t>
+          <t>-49.3728646</t>
         </is>
       </c>
       <c r="F773" t="inlineStr">
         <is>
-          <t>2301520 000027/2023</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>DPEI-9447050</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>9447050</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -23396,23 +23396,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D774" t="inlineStr"/>
-      <c r="E774" t="inlineStr"/>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>-19.70009506319273</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>-49.31984772214537</t>
+        </is>
+      </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>9468321</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -23420,31 +23428,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr">
-        <is>
-          <t>-21.822481</t>
-        </is>
-      </c>
-      <c r="E775" t="inlineStr">
-        <is>
-          <t>-43.319474</t>
-        </is>
-      </c>
+      <c r="D775" t="inlineStr"/>
+      <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr">
         <is>
-          <t>2301520 000007/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -23452,31 +23452,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr">
-        <is>
-          <t>-19.8898481</t>
-        </is>
-      </c>
-      <c r="E776" t="inlineStr">
-        <is>
-          <t>-49.3728646</t>
-        </is>
-      </c>
+      <c r="D776" t="inlineStr"/>
+      <c r="E776" t="inlineStr"/>
       <c r="F776" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>AEST-9441233/2024</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9441233</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -23484,31 +23476,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D777" t="inlineStr">
-        <is>
-          <t>-19.70009506319273</t>
-        </is>
-      </c>
-      <c r="E777" t="inlineStr">
-        <is>
-          <t>-49.31984772214537</t>
-        </is>
-      </c>
+      <c r="D777" t="inlineStr"/>
+      <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>2301931 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -23520,19 +23504,19 @@
       <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -23540,23 +23524,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr"/>
-      <c r="E779" t="inlineStr"/>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>-16.060571</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>-45.14998800000001</t>
+        </is>
+      </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>AEST-9441233/2024</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>9441233</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -23564,23 +23556,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr"/>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>-16.12398555419337</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>-45.72443570435887</t>
+        </is>
+      </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>2301931 000002/2024</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -23588,23 +23588,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D781" t="inlineStr"/>
-      <c r="E781" t="inlineStr"/>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>-18.58543851687659</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>-42.49387848441415</t>
+        </is>
+      </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -23614,29 +23622,29 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>-16.060571</t>
+          <t>-18.45181382097735</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>-45.14998800000001</t>
+          <t>-42.61418109121731</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9491013</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -23646,29 +23654,29 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>-16.12398555419337</t>
+          <t>-19.422927421098</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>-45.72443570435887</t>
+          <t>-44.54875745320115</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301520 000028/2025</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -23678,29 +23686,29 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>-18.58543851687659</t>
+          <t>-18.3540804218777</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>-42.49387848441415</t>
+          <t>-48.23074551265237</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -23710,29 +23718,29 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>-18.45181382097735</t>
+          <t>-18.5342387</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>-42.61418109121731</t>
+          <t>-48.1962378</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>9491013</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -23740,31 +23748,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr">
-        <is>
-          <t>-19.422927421098</t>
-        </is>
-      </c>
-      <c r="E786" t="inlineStr">
-        <is>
-          <t>-44.54875745320115</t>
-        </is>
-      </c>
+      <c r="D786" t="inlineStr"/>
+      <c r="E786" t="inlineStr"/>
       <c r="F786" t="inlineStr">
         <is>
-          <t>2301520 000028/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9430925</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -23774,29 +23774,29 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>-18.3540804218777</t>
+          <t>-17.21201507063193</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>-48.23074551265237</t>
+          <t>-46.68787211434018</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>1301606 000003/2023</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9430925</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -23806,41 +23806,49 @@
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>-18.5342387</t>
+          <t>-17.10715545158019</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
         <is>
-          <t>-48.1962378</t>
+          <t>-46.62095644997671</t>
         </is>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>1301606 000003/2023</t>
         </is>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9430925</t>
         </is>
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D789" t="inlineStr"/>
-      <c r="E789" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>-17.10715545158019</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>-46.62095644997671</t>
+        </is>
+      </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>1301606 000003/2023</t>
         </is>
       </c>
     </row>
@@ -23857,17 +23865,17 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>-17.21201507063193</t>
+          <t>-17.03493425248441</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>-46.68787211434018</t>
+          <t>-46.5886262006665</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
@@ -23879,12 +23887,12 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>DOV-003/2022-A</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>9430925</t>
+          <t>9344739</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
@@ -23892,119 +23900,111 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D791" t="inlineStr">
-        <is>
-          <t>-17.10715545158019</t>
-        </is>
-      </c>
-      <c r="E791" t="inlineStr">
-        <is>
-          <t>-46.62095644997671</t>
-        </is>
-      </c>
+      <c r="D791" t="inlineStr"/>
+      <c r="E791" t="inlineStr"/>
       <c r="F791" t="inlineStr">
         <is>
-          <t>1301606 000003/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>PRC-29.008/2017-ANO 4</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>9430925</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>-17.10715545158019</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>-46.62095644997671</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>1301606 000003/2023</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>DC-9441306/2024</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>9430925</t>
+          <t>9441306</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>-17.03493425248441</t>
+          <t>-15.600402</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">
         <is>
-          <t>-46.5886262006665</t>
+          <t>-42.543776</t>
         </is>
       </c>
       <c r="F793" t="inlineStr">
         <is>
-          <t>1301606 000003/2023</t>
+          <t>2301520 000012/2024</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>DOV-003/2022-A</t>
-        </is>
-      </c>
-      <c r="B794" t="inlineStr">
-        <is>
-          <t>9344739</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC-9441355/2024 </t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr"/>
       <c r="C794" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D794" t="inlineStr"/>
-      <c r="E794" t="inlineStr"/>
-      <c r="F794" t="inlineStr">
-        <is>
-          <t>2301901 000009/2021</t>
-        </is>
-      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>-17.82651719999999</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>-41.506751</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr"/>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-ANO 4</t>
+          <t>DC-9445950/2024</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9445950</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -24014,29 +24014,29 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-19.779781</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-44.23890900000001</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>DC-9441306/2024</t>
+          <t>DC-9445950/2024</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>9441306</t>
+          <t>9445950</t>
         </is>
       </c>
       <c r="C796" t="inlineStr">
@@ -24046,27 +24046,31 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>-15.600402</t>
+          <t>-19.83023</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>-42.543776</t>
+          <t>-44.18012</t>
         </is>
       </c>
       <c r="F796" t="inlineStr">
         <is>
-          <t>2301520 000012/2024</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-9441355/2024 </t>
-        </is>
-      </c>
-      <c r="B797" t="inlineStr"/>
+          <t>DC-9445591/2024</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>9445591</t>
+        </is>
+      </c>
       <c r="C797" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -24074,25 +24078,29 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>-17.82651719999999</t>
+          <t>-17.96127463110632</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>-41.506751</t>
-        </is>
-      </c>
-      <c r="F797" t="inlineStr"/>
+          <t>-46.42781545395799</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>2301520 002220/2024</t>
+        </is>
+      </c>
     </row>
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>DC-9445950/2024</t>
+          <t>DC-9445591/2024</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>9445950</t>
+          <t>9445591</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -24102,12 +24110,12 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>-19.779781</t>
+          <t>-18.65274465135498</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>-44.23890900000001</t>
+          <t>-46.59916240618842</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
@@ -24119,12 +24127,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>DC-9445950/2024</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>9445950</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -24132,31 +24140,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D799" t="inlineStr">
-        <is>
-          <t>-19.83023</t>
-        </is>
-      </c>
-      <c r="E799" t="inlineStr">
-        <is>
-          <t>-44.18012</t>
-        </is>
-      </c>
+      <c r="D799" t="inlineStr"/>
+      <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>DC-9445591/2024</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>9445591</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -24164,31 +24164,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr">
-        <is>
-          <t>-17.96127463110632</t>
-        </is>
-      </c>
-      <c r="E800" t="inlineStr">
-        <is>
-          <t>-46.42781545395799</t>
-        </is>
-      </c>
+      <c r="D800" t="inlineStr"/>
+      <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>DC-9445591/2024</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>9445591</t>
+          <t>9473312</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -24196,31 +24188,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D801" t="inlineStr">
-        <is>
-          <t>-18.65274465135498</t>
-        </is>
-      </c>
-      <c r="E801" t="inlineStr">
-        <is>
-          <t>-46.59916240618842</t>
-        </is>
-      </c>
+      <c r="D801" t="inlineStr"/>
+      <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301762 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -24228,23 +24212,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D802" t="inlineStr"/>
-      <c r="E802" t="inlineStr"/>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>-18.694272</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>-43.434571</t>
+        </is>
+      </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -24252,23 +24244,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr"/>
-      <c r="E803" t="inlineStr"/>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>-19.0126003</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>-43.4419084</t>
+        </is>
+      </c>
       <c r="F803" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DOV-005/2022-B</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>9473312</t>
+          <t>9344755</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -24276,23 +24276,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D804" t="inlineStr"/>
-      <c r="E804" t="inlineStr"/>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>-18.95121</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>-41.9528346</t>
+        </is>
+      </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>2301762 000004/2025</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -24302,29 +24310,29 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>-18.694272</t>
+          <t>-14.7566423</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>-43.434571</t>
+          <t>-43.9321579</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -24332,31 +24340,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D806" t="inlineStr">
-        <is>
-          <t>-19.0126003</t>
-        </is>
-      </c>
-      <c r="E806" t="inlineStr">
-        <is>
-          <t>-43.4419084</t>
-        </is>
-      </c>
+      <c r="D806" t="inlineStr"/>
+      <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>DOV-005/2022-B</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>9344755</t>
+          <t>9478941</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -24364,31 +24364,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D807" t="inlineStr">
-        <is>
-          <t>-18.95121</t>
-        </is>
-      </c>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>-41.9528346</t>
-        </is>
-      </c>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
       <c r="F807" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DOV-004/2021-A</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -24398,29 +24390,29 @@
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>-14.7566423</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
         <is>
-          <t>-43.9321579</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F808" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DOV-003/2021-A</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -24432,19 +24424,19 @@
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>DPEI-9478941/2025</t>
+          <t>DM-22.009/2020-D</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>9478941</t>
+          <t>9245587</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -24452,23 +24444,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>-20.405398</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>-42.886629</t>
+        </is>
+      </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301762 000042/2019</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>DOV-004/2021-A</t>
+          <t>DM-22.012/2020-D</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9245580</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -24478,29 +24478,29 @@
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-20.735033</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-46.6045231</t>
         </is>
       </c>
       <c r="F811" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000043/2019</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>DOV-003/2021-A</t>
+          <t>DM-009/2022-B</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9327308</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -24508,23 +24508,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D812" t="inlineStr"/>
-      <c r="E812" t="inlineStr"/>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>-20.350449</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>-41.9526169</t>
+        </is>
+      </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000087/2021</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-D</t>
+          <t>DP-012/2023</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>9245587</t>
+          <t>9386092</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -24532,31 +24540,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D813" t="inlineStr">
-        <is>
-          <t>-20.405398</t>
-        </is>
-      </c>
-      <c r="E813" t="inlineStr">
-        <is>
-          <t>-42.886629</t>
-        </is>
-      </c>
+      <c r="D813" t="inlineStr"/>
+      <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr">
         <is>
-          <t>2301762 000042/2019</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-D</t>
+          <t>DOV-004/2021-B</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>9245580</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -24566,29 +24566,29 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>-20.735033</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>-46.6045231</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>2301762 000043/2019</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>DM-009/2022-B</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>9327308</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -24596,31 +24596,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D815" t="inlineStr">
-        <is>
-          <t>-20.350449</t>
-        </is>
-      </c>
-      <c r="E815" t="inlineStr">
-        <is>
-          <t>-41.9526169</t>
-        </is>
-      </c>
+      <c r="D815" t="inlineStr"/>
+      <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr">
         <is>
-          <t>2301762 000087/2021</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>DP-012/2023</t>
+          <t>DC-007/2024</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>9386092</t>
+          <t>9424592</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -24632,19 +24624,19 @@
       <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301520 000024/2023</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>DOV-004/2021-B</t>
+          <t>DM-010/2024</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -24652,31 +24644,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D817" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E817" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D817" t="inlineStr"/>
+      <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DPEI-001/2024</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9414354</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -24684,23 +24668,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D818" t="inlineStr"/>
-      <c r="E818" t="inlineStr"/>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>-18.5967086</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>-46.51810469999999</t>
+        </is>
+      </c>
       <c r="F818" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>DC-007/2024</t>
+          <t>DC-010/2024</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>9424592</t>
+          <t>9426807</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -24708,23 +24700,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>-20.39729542216063</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>-42.37959570001862</t>
+        </is>
+      </c>
       <c r="F819" t="inlineStr">
         <is>
-          <t>2301520 000024/2023</t>
+          <t>2301520 000029/2023</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>DM-010/2024</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -24736,19 +24736,19 @@
       <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>DPEI-001/2024</t>
+          <t>DOV-003/2021-B</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>9414354</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -24756,31 +24756,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr">
-        <is>
-          <t>-18.5967086</t>
-        </is>
-      </c>
-      <c r="E821" t="inlineStr">
-        <is>
-          <t>-46.51810469999999</t>
-        </is>
-      </c>
+      <c r="D821" t="inlineStr"/>
+      <c r="E821" t="inlineStr"/>
       <c r="F821" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>DC-010/2024</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>9426807</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -24788,31 +24780,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>-20.39729542216063</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>-42.37959570001862</t>
-        </is>
-      </c>
+      <c r="D822" t="inlineStr"/>
+      <c r="E822" t="inlineStr"/>
       <c r="F822" t="inlineStr">
         <is>
-          <t>2301520 000029/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -24820,23 +24804,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr"/>
-      <c r="E823" t="inlineStr"/>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>DOV-003/2021-B</t>
+          <t>DG/AMA-009436677/2024</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9436677</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -24848,19 +24840,19 @@
       <c r="E824" t="inlineStr"/>
       <c r="F824" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301617 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DOV-001/2021-B</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -24868,23 +24860,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D825" t="inlineStr"/>
-      <c r="E825" t="inlineStr"/>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -24892,31 +24892,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D826" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E826" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D826" t="inlineStr"/>
+      <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>DG/AMA-009436677/2024</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>9436677</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -24924,23 +24916,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D827" t="inlineStr"/>
-      <c r="E827" t="inlineStr"/>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>-19.96402458305301</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>-44.72983589212661</t>
+        </is>
+      </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>2301617 000002/2024</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>DOV-001/2021-B</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -24950,29 +24950,29 @@
       </c>
       <c r="D828" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E828" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>DOV-002/2021-B</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>DOV-002/2021-B</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -24980,23 +24980,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D829" t="inlineStr"/>
-      <c r="E829" t="inlineStr"/>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -25006,29 +25014,29 @@
       </c>
       <c r="D830" t="inlineStr">
         <is>
-          <t>-19.96402458305301</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E830" t="inlineStr">
         <is>
-          <t>-44.72983589212661</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -25055,12 +25063,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -25070,29 +25078,29 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.7469167</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-47.9483714</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -25100,107 +25108,107 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D833" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E833" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D833" t="inlineStr"/>
+      <c r="E833" t="inlineStr"/>
       <c r="F833" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
         <is>
-          <t>-19.7469167</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E835" t="inlineStr">
         <is>
-          <t>-47.9483714</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F835" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D836" t="inlineStr"/>
-      <c r="E836" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>-17.03493425248546</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>-46.58862620066699</t>
+        </is>
+      </c>
       <c r="F836" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
@@ -25222,12 +25230,12 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25249,17 +25257,17 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25281,17 +25289,17 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25313,7 +25321,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
@@ -25345,17 +25353,17 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25367,108 +25375,100 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D842" t="inlineStr">
-        <is>
-          <t>-17.03493425248546</t>
-        </is>
-      </c>
-      <c r="E842" t="inlineStr">
-        <is>
-          <t>-46.58862620066699</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr"/>
+      <c r="E842" t="inlineStr"/>
       <c r="F842" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-15.483562</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-44.39677500000001</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-15.5007309</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-44.7624674</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25478,29 +25478,29 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25510,29 +25510,29 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25542,29 +25542,29 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25572,31 +25572,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr">
-        <is>
-          <t>-17.21201508102213</t>
-        </is>
-      </c>
-      <c r="E848" t="inlineStr">
-        <is>
-          <t>-46.687872082284</t>
-        </is>
-      </c>
+      <c r="D848" t="inlineStr"/>
+      <c r="E848" t="inlineStr"/>
       <c r="F848" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25604,31 +25596,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr">
-        <is>
-          <t>-17.10715545158923</t>
-        </is>
-      </c>
-      <c r="E849" t="inlineStr">
-        <is>
-          <t>-46.62095644999281</t>
-        </is>
-      </c>
+      <c r="D849" t="inlineStr"/>
+      <c r="E849" t="inlineStr"/>
       <c r="F849" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C850" t="inlineStr">
@@ -25636,31 +25620,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr">
-        <is>
-          <t>-17.10715545158923</t>
-        </is>
-      </c>
-      <c r="E850" t="inlineStr">
-        <is>
-          <t>-46.62095644999281</t>
-        </is>
-      </c>
+      <c r="D850" t="inlineStr"/>
+      <c r="E850" t="inlineStr"/>
       <c r="F850" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C851" t="inlineStr">
@@ -25668,31 +25644,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr">
-        <is>
-          <t>-17.10715545158923</t>
-        </is>
-      </c>
-      <c r="E851" t="inlineStr">
-        <is>
-          <t>-46.62095644999281</t>
-        </is>
-      </c>
+      <c r="D851" t="inlineStr"/>
+      <c r="E851" t="inlineStr"/>
       <c r="F851" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25702,77 +25670,93 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D853" t="inlineStr"/>
-      <c r="E853" t="inlineStr"/>
-      <c r="F853" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>-21.27464910003665</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>-42.91331545001727</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>2301520 000005/2026</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-21.23264738347681</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr"/>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>2301520 000005/2026</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25782,25 +25766,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-21.23528484003703</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
-      <c r="F855" t="inlineStr"/>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>2301520 000005/2026</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25810,93 +25798,69 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.6107675</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-42.64891799999999</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
-        </is>
-      </c>
-      <c r="B857" t="inlineStr">
-        <is>
-          <t>9482046</t>
-        </is>
-      </c>
+          <t>DC-9518942/2026</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr"/>
       <c r="C857" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E857" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F857" t="inlineStr">
-        <is>
-          <t>2301901 000001/2025</t>
-        </is>
-      </c>
+      <c r="D857" t="inlineStr"/>
+      <c r="E857" t="inlineStr"/>
+      <c r="F857" t="inlineStr"/>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E858" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
+      <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25904,23 +25868,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25932,19 +25904,19 @@
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25956,19 +25928,19 @@
       <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25976,23 +25948,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -26004,19 +25984,19 @@
       <c r="E863" t="inlineStr"/>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -26028,21 +26008,17 @@
       <c r="E864" t="inlineStr"/>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr"/>
       <c r="C865" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26050,21 +26026,17 @@
       </c>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="F865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26076,19 +26048,19 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C867" t="inlineStr">
@@ -26098,109 +26070,117 @@
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
-      <c r="F867" t="inlineStr"/>
+          <t>-43.8541147</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>2301762 000004/2026</t>
+        </is>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
-        </is>
-      </c>
-      <c r="F868" t="inlineStr"/>
+          <t>-50.219328</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>1301606 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D869" t="inlineStr">
-        <is>
-          <t>-21.23264738347681</t>
-        </is>
-      </c>
-      <c r="E869" t="inlineStr">
-        <is>
-          <t>-43.43361939286979</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr"/>
+      <c r="E869" t="inlineStr"/>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>2301762 000001/2026</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
-      <c r="F870" t="inlineStr"/>
+          <t>-43.983328</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2301901 000003/2021</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9519020</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26208,51 +26188,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>-19.6107675</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>-42.64891799999999</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr"/>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D872" t="inlineStr"/>
-      <c r="E872" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26262,29 +26246,29 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
+          <t>-43.8541147</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26292,23 +26276,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D874" t="inlineStr"/>
-      <c r="E874" t="inlineStr"/>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26316,23 +26308,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr"/>
-      <c r="E875" t="inlineStr"/>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
@@ -26340,31 +26340,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E876" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
       <c r="F876" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -26376,19 +26368,19 @@
       <c r="E877" t="inlineStr"/>
       <c r="F877" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26400,17 +26392,21 @@
       <c r="E878" t="inlineStr"/>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C879" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26418,37 +26414,53 @@
       </c>
       <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr"/>
-      <c r="F879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
-      <c r="F880" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>9512043</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -26458,57 +26470,61 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-16.11921421383736</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr"/>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>-19.747173</t>
+          <t>-16.12119845072</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>-50.219328</t>
+          <t>-45.6488268407393</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9512044</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26518,49 +26534,45 @@
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2301520 000036/2025</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E884" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr"/>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26572,19 +26584,19 @@
       <c r="E885" t="inlineStr"/>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26592,16 +26604,8 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E886" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
       <c r="F886" t="inlineStr">
         <is>
           <t>2301762 000051/2023</t>
@@ -26611,12 +26615,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26624,31 +26628,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E887" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -26658,29 +26654,29 @@
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-17.8518635</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-41.5076927</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26690,53 +26686,53 @@
       </c>
       <c r="D889" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-20.6829764</t>
         </is>
       </c>
       <c r="E889" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.8232506</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr"/>
       <c r="F890" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -26748,67 +26744,67 @@
       <c r="E891" t="inlineStr"/>
       <c r="F891" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr"/>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9511902/2026</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9511902</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr"/>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301520 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-9519034/2026</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9519034</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -26820,19 +26816,19 @@
       <c r="E894" t="inlineStr"/>
       <c r="F894" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000028/2025</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9519017/2026</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9519017</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -26840,469 +26836,21 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr"/>
-      <c r="E895" t="inlineStr"/>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>-18.46005275010656</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>-48.18218127247928</t>
+        </is>
+      </c>
       <c r="F895" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="896">
-      <c r="A896" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B896" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C896" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D896" t="inlineStr"/>
-      <c r="E896" t="inlineStr"/>
-      <c r="F896" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="897">
-      <c r="A897" t="inlineStr">
-        <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B897" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
-      <c r="C897" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D897" t="inlineStr"/>
-      <c r="E897" t="inlineStr"/>
-      <c r="F897" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="898">
-      <c r="A898" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B898" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C898" t="inlineStr">
-        <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D898" t="inlineStr">
-        <is>
-          <t>-16.11741660736296</t>
-        </is>
-      </c>
-      <c r="E898" t="inlineStr">
-        <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
-      <c r="F898" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B899" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C899" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D899" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E899" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
-      <c r="F899" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="900">
-      <c r="A900" t="inlineStr">
-        <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B900" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
-      <c r="C900" t="inlineStr">
-        <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D900" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E900" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
-      <c r="F900" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="901">
-      <c r="A901" t="inlineStr">
-        <is>
-          <t>DC-9493529/2026</t>
-        </is>
-      </c>
-      <c r="B901" t="inlineStr">
-        <is>
-          <t>9493529</t>
-        </is>
-      </c>
-      <c r="C901" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D901" t="inlineStr"/>
-      <c r="E901" t="inlineStr"/>
-      <c r="F901" t="inlineStr">
-        <is>
-          <t>2301520 000036/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="902">
-      <c r="A902" t="inlineStr">
-        <is>
-          <t>DM-012/2024-A</t>
-        </is>
-      </c>
-      <c r="B902" t="inlineStr">
-        <is>
-          <t>9422079</t>
-        </is>
-      </c>
-      <c r="C902" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D902" t="inlineStr"/>
-      <c r="E902" t="inlineStr"/>
-      <c r="F902" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr">
-        <is>
-          <t>DM-9502116/2026</t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr">
-        <is>
-          <t>9502116</t>
-        </is>
-      </c>
-      <c r="C903" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D903" t="inlineStr"/>
-      <c r="E903" t="inlineStr"/>
-      <c r="F903" t="inlineStr">
-        <is>
-          <t>2301762 000026/2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr">
-        <is>
-          <t>DM-018/2024-A</t>
-        </is>
-      </c>
-      <c r="B904" t="inlineStr">
-        <is>
-          <t>9424304</t>
-        </is>
-      </c>
-      <c r="C904" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D904" t="inlineStr"/>
-      <c r="E904" t="inlineStr"/>
-      <c r="F904" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="905">
-      <c r="A905" t="inlineStr">
-        <is>
-          <t>DM-016/2024-A</t>
-        </is>
-      </c>
-      <c r="B905" t="inlineStr">
-        <is>
-          <t>9424337</t>
-        </is>
-      </c>
-      <c r="C905" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D905" t="inlineStr"/>
-      <c r="E905" t="inlineStr"/>
-      <c r="F905" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="906">
-      <c r="A906" t="inlineStr">
-        <is>
-          <t>DM-020/2024-A</t>
-        </is>
-      </c>
-      <c r="B906" t="inlineStr">
-        <is>
-          <t>9427674</t>
-        </is>
-      </c>
-      <c r="C906" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D906" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E906" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
-      <c r="F906" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="907">
-      <c r="A907" t="inlineStr">
-        <is>
-          <t>DM-022/2024-A</t>
-        </is>
-      </c>
-      <c r="B907" t="inlineStr">
-        <is>
-          <t>9427765</t>
-        </is>
-      </c>
-      <c r="C907" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D907" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E907" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
-      <c r="F907" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B908" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="C908" t="inlineStr">
-        <is>
-          <t>Obra 4</t>
-        </is>
-      </c>
-      <c r="D908" t="inlineStr"/>
-      <c r="E908" t="inlineStr"/>
-      <c r="F908" t="inlineStr"/>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B909" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="C909" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D909" t="inlineStr"/>
-      <c r="E909" t="inlineStr"/>
-      <c r="F909" t="inlineStr"/>
-    </row>
-    <row r="910">
-      <c r="A910" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B910" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="C910" t="inlineStr">
-        <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D910" t="inlineStr"/>
-      <c r="E910" t="inlineStr"/>
-      <c r="F910" t="inlineStr"/>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr">
-        <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B911" t="inlineStr">
-        <is>
-          <t>9511902</t>
-        </is>
-      </c>
-      <c r="C911" t="inlineStr">
-        <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D911" t="inlineStr"/>
-      <c r="E911" t="inlineStr"/>
-      <c r="F911" t="inlineStr"/>
-    </row>
-    <row r="912">
-      <c r="A912" t="inlineStr">
-        <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
-      <c r="B912" t="inlineStr">
-        <is>
-          <t>9519034</t>
-        </is>
-      </c>
-      <c r="C912" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D912" t="inlineStr"/>
-      <c r="E912" t="inlineStr"/>
-      <c r="F912" t="inlineStr"/>
-    </row>
-    <row r="913">
-      <c r="A913" t="inlineStr">
-        <is>
-          <t>DC-9519017/2026</t>
-        </is>
-      </c>
-      <c r="B913" t="inlineStr">
-        <is>
-          <t>9519017</t>
-        </is>
-      </c>
-      <c r="C913" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D913" t="inlineStr">
-        <is>
-          <t>-18.46005275010656</t>
-        </is>
-      </c>
-      <c r="E913" t="inlineStr">
-        <is>
-          <t>-48.18218127247928</t>
-        </is>
-      </c>
-      <c r="F913" t="inlineStr"/>
+          <t>2301520 000017/2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F895"/>
+  <dimension ref="A1:F901"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19983,12 +19983,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>DC-9447109/2024</t>
+          <t>9439923</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>9447109</t>
+          <t>9439923</t>
         </is>
       </c>
       <c r="C654" t="inlineStr">
@@ -19998,17 +19998,17 @@
       </c>
       <c r="D654" t="inlineStr">
         <is>
-          <t>-14.757046772025067</t>
+          <t>-19.5952902</t>
         </is>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>-43.93015192008537</t>
+          <t>-46.9326049</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>2301520 000021/2024</t>
+          <t>2301707 000004/2024</t>
         </is>
       </c>
     </row>
@@ -20030,12 +20030,12 @@
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>-19.783357402903007</t>
+          <t>-14.757046772025067</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>-43.951944370919506</t>
+          <t>-43.93015192008537</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
@@ -20047,12 +20047,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>DC-9445587/2024</t>
+          <t>DC-9447109/2024</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>9445587</t>
+          <t>9447109</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
@@ -20062,17 +20062,17 @@
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>-20.63168865721149</t>
+          <t>-19.783357402903007</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>-47.10193369380541</t>
+          <t>-43.951944370919506</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301520 000021/2024</t>
         </is>
       </c>
     </row>
@@ -20094,12 +20094,12 @@
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>-20.6041089</t>
+          <t>-20.63168865721149</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>-46.9106488</t>
+          <t>-47.10193369380541</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
@@ -20111,12 +20111,12 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>DC-9472752/2025</t>
+          <t>DC-9445587/2024</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>9472752</t>
+          <t>9445587</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20126,17 +20126,17 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>-20.05185754871156</t>
+          <t>-20.6041089</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>-44.18814551429173</t>
+          <t>-46.9106488</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>2301520 000008/2025</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
@@ -20158,12 +20158,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>-20.130347305381726</t>
+          <t>-20.05185754871156</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>-44.19984053737846</t>
+          <t>-44.18814551429173</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
@@ -20185,17 +20185,17 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>-20.042186156631548</t>
+          <t>-20.130347305381726</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>-44.198824969508905</t>
+          <t>-44.19984053737846</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
@@ -20222,12 +20222,12 @@
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>-20.009247062372893</t>
+          <t>-20.042186156631548</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>-44.204977569705186</t>
+          <t>-44.198824969508905</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
@@ -20239,36 +20239,44 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>DM-008/2024</t>
+          <t>DC-9472752/2025</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9472752</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-20.009247062372893</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>-44.204977569705186</t>
+        </is>
+      </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000008/2025</t>
         </is>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>DC-006/2024</t>
+          <t>DM-008/2024</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>9422285</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -20276,31 +20284,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
-        <is>
-          <t>-17.0321536895841</t>
-        </is>
-      </c>
-      <c r="E663" t="inlineStr">
-        <is>
-          <t>-46.014676019311956</t>
-        </is>
-      </c>
+      <c r="D663" t="inlineStr"/>
+      <c r="E663" t="inlineStr"/>
       <c r="F663" t="inlineStr">
         <is>
-          <t>2301520 000016/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>DM-007/2024</t>
+          <t>DC-006/2024</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>9422060</t>
+          <t>9422285</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -20308,23 +20308,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr"/>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-17.0321536895841</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>-46.014676019311956</t>
+        </is>
+      </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000016/2023</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>DM-9437231</t>
+          <t>DM-007/2024</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>9437231</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -20336,19 +20344,19 @@
       <c r="E665" t="inlineStr"/>
       <c r="F665" t="inlineStr">
         <is>
-          <t>2301762 000006/2024</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>9442805</t>
+          <t>DM-9437231</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>9442805</t>
+          <t>9437231</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -20360,19 +20368,19 @@
       <c r="E666" t="inlineStr"/>
       <c r="F666" t="inlineStr">
         <is>
-          <t>2301403 000099/2024</t>
+          <t>2301762 000006/2024</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>DPEI-9447985</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>9447985</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -20380,31 +20388,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
-        <is>
-          <t>-19.9149659</t>
-        </is>
-      </c>
-      <c r="E667" t="inlineStr">
-        <is>
-          <t>-43.9000041</t>
-        </is>
-      </c>
+      <c r="D667" t="inlineStr"/>
+      <c r="E667" t="inlineStr"/>
       <c r="F667" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301403 000099/2024</t>
         </is>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>DM-9452477/2025</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>9452477</t>
+          <t>9442805</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -20416,19 +20416,19 @@
       <c r="E668" t="inlineStr"/>
       <c r="F668" t="inlineStr">
         <is>
-          <t>2301762 000019/2024</t>
+          <t>2301403 000099/2024</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>DER-30.014/2025</t>
+          <t>DPEI-9447985</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>DER-30.014/2025</t>
+          <t>9447985</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -20436,23 +20436,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr"/>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-19.9149659</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-43.9000041</t>
+        </is>
+      </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>DM-002/2024-B</t>
+          <t>DM-9452477/2025</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>9410208</t>
+          <t>9452477</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -20460,31 +20468,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr">
-        <is>
-          <t>-19.638615</t>
-        </is>
-      </c>
-      <c r="E670" t="inlineStr">
-        <is>
-          <t>-43.228648</t>
-        </is>
-      </c>
+      <c r="D670" t="inlineStr"/>
+      <c r="E670" t="inlineStr"/>
       <c r="F670" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301762 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>DC-9492715/2025</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>9492715</t>
+          <t>DER-30.014/2025</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -20492,31 +20492,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr">
-        <is>
-          <t>-15.97197985837174</t>
-        </is>
-      </c>
-      <c r="E671" t="inlineStr">
-        <is>
-          <t>-44.90024660668323</t>
-        </is>
-      </c>
+      <c r="D671" t="inlineStr"/>
+      <c r="E671" t="inlineStr"/>
       <c r="F671" t="inlineStr">
         <is>
-          <t>2301520 000035/2025</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>DOV-002/2021-A</t>
+          <t>DM-002/2024-B</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>9292040</t>
+          <t>9410208</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
@@ -20524,23 +20516,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr"/>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-19.638615</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-43.228648</t>
+        </is>
+      </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>DM-026/2023-A</t>
+          <t>DC-9492715/2025</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>9407068</t>
+          <t>9492715</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
@@ -20548,23 +20548,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-15.97197985837174</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-44.90024660668323</t>
+        </is>
+      </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301520 000035/2025</t>
         </is>
       </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>DM-025/2023-A</t>
+          <t>DOV-002/2021-A</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9292040</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
@@ -20576,19 +20584,19 @@
       <c r="E674" t="inlineStr"/>
       <c r="F674" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>DOV-002/2022-B</t>
+          <t>DM-026/2023-A</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>9344727</t>
+          <t>9407068</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -20600,19 +20608,19 @@
       <c r="E675" t="inlineStr"/>
       <c r="F675" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>DM-030/2023-B</t>
+          <t>DM-025/2023-A</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>9408491</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -20620,16 +20628,8 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr">
-        <is>
-          <t>-19.5068923</t>
-        </is>
-      </c>
-      <c r="E676" t="inlineStr">
-        <is>
-          <t>-42.6044222</t>
-        </is>
-      </c>
+      <c r="D676" t="inlineStr"/>
+      <c r="E676" t="inlineStr"/>
       <c r="F676" t="inlineStr">
         <is>
           <t>2301762 000027/2023</t>
@@ -20639,12 +20639,12 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DOV-002/2022-B</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9344727</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
@@ -20652,31 +20652,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr">
-        <is>
-          <t>-20.4799694</t>
-        </is>
-      </c>
-      <c r="E677" t="inlineStr">
-        <is>
-          <t>-45.79996939999999</t>
-        </is>
-      </c>
+      <c r="D677" t="inlineStr"/>
+      <c r="E677" t="inlineStr"/>
       <c r="F677" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>DC-9492065/2025</t>
+          <t>DM-030/2023-B</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>9492065</t>
+          <t>9408491</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
@@ -20686,29 +20678,29 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>-20.759954</t>
+          <t>-19.5068923</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>-45.918453</t>
+          <t>-42.6044222</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>2301520 000023/2025</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>DM-025/2023-B</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>9408445</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
@@ -20718,29 +20710,29 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>-16.8555088</t>
+          <t>-20.4799694</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>-42.0630933</t>
+          <t>-45.79996939999999</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>DOV-003/2022-B</t>
+          <t>DC-9492065/2025</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>9344739</t>
+          <t>9492065</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
@@ -20750,29 +20742,29 @@
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>-18.5967086</t>
+          <t>-20.759954</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>-46.5181047</t>
+          <t>-45.918453</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000023/2025</t>
         </is>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>DM-029/2023-B</t>
+          <t>DM-025/2023-B</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>9408476</t>
+          <t>9408445</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -20782,12 +20774,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>-17.701729</t>
+          <t>-16.8555088</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>-42.515515</t>
+          <t>-42.0630933</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
@@ -20799,12 +20791,12 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>DM-026/2023-B</t>
+          <t>DOV-003/2022-B</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>9407068</t>
+          <t>9344739</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -20814,53 +20806,61 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>-16.00026</t>
+          <t>-18.5967086</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>-41.279238</t>
+          <t>-46.5181047</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DM-029/2023-B</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9408476</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-17.701729</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-42.515515</t>
+        </is>
+      </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>DOV-001/2022-A</t>
+          <t>DM-026/2023-B</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9407068</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -20868,55 +20868,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr"/>
-      <c r="E684" t="inlineStr"/>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-16.00026</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-41.279238</t>
+        </is>
+      </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DC-005/2024</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>9422256</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>-19.58691270347314</t>
-        </is>
-      </c>
-      <c r="E685" t="inlineStr">
-        <is>
-          <t>-47.0726885458534</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr"/>
+      <c r="E685" t="inlineStr"/>
       <c r="F685" t="inlineStr">
         <is>
-          <t>2301520 000025/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>DC-005/2024</t>
+          <t>DOV-001/2022-A</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>9422256</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
@@ -20924,31 +20924,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr">
-        <is>
-          <t>-19.528005598761357</t>
-        </is>
-      </c>
-      <c r="E686" t="inlineStr">
-        <is>
-          <t>-47.07955421284039</t>
-        </is>
-      </c>
+      <c r="D686" t="inlineStr"/>
+      <c r="E686" t="inlineStr"/>
       <c r="F686" t="inlineStr">
         <is>
-          <t>2301520 000025/2023</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>DOV-002/2022-A</t>
+          <t>DC-005/2024</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>9344727</t>
+          <t>9422256</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
@@ -20956,23 +20948,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-19.58691270347314</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-47.0726885458534</t>
+        </is>
+      </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000025/2023</t>
         </is>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>AMA-9445113/2024</t>
+          <t>DC-005/2024</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>9445113</t>
+          <t>9422256</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
@@ -20980,23 +20980,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-19.528005598761357</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-47.07955421284039</t>
+        </is>
+      </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>2301617 000001/2024</t>
+          <t>2301520 000025/2023</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>DM-001/2024-A</t>
+          <t>DOV-002/2022-A</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>9410177</t>
+          <t>9344727</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -21008,19 +21016,19 @@
       <c r="E689" t="inlineStr"/>
       <c r="F689" t="inlineStr">
         <is>
-          <t>2301762 000001/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-D</t>
+          <t>AMA-9445113/2024</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9445113</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -21028,31 +21036,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D690" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E690" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D690" t="inlineStr"/>
+      <c r="E690" t="inlineStr"/>
       <c r="F690" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301617 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>DM-9445781/2024</t>
+          <t>DM-001/2024-A</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>9445781</t>
+          <t>9410177</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -21064,19 +21064,19 @@
       <c r="E691" t="inlineStr"/>
       <c r="F691" t="inlineStr">
         <is>
-          <t>2301762 000015/2024</t>
+          <t>2301762 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>DM-9445821/2024</t>
+          <t>PRC-29.008/2017-D</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>9445821</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
@@ -21084,23 +21084,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D692" t="inlineStr"/>
-      <c r="E692" t="inlineStr"/>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>2301762 000012/2024</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>DM-9447456/2024</t>
+          <t>DM-9445781/2024</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>9447456</t>
+          <t>9445781</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
@@ -21112,19 +21120,19 @@
       <c r="E693" t="inlineStr"/>
       <c r="F693" t="inlineStr">
         <is>
-          <t>2301762 000017/2024</t>
+          <t>2301762 000015/2024</t>
         </is>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>DOV-004/2022-B</t>
+          <t>DM-9445821/2024</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>9344750</t>
+          <t>9445821</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
@@ -21136,19 +21144,19 @@
       <c r="E694" t="inlineStr"/>
       <c r="F694" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301762 000012/2024</t>
         </is>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>DM-028/2023-A</t>
+          <t>DM-9447456/2024</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>9408646</t>
+          <t>9447456</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
@@ -21160,19 +21168,19 @@
       <c r="E695" t="inlineStr"/>
       <c r="F695" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301762 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>DPEI-9446143</t>
+          <t>DOV-004/2022-B</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>9446143</t>
+          <t>9344750</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
@@ -21184,19 +21192,19 @@
       <c r="E696" t="inlineStr"/>
       <c r="F696" t="inlineStr">
         <is>
-          <t>2301601 000004/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>DM-9474704/2025</t>
+          <t>DM-028/2023-A</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>9474704</t>
+          <t>9408646</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
@@ -21208,19 +21216,19 @@
       <c r="E697" t="inlineStr"/>
       <c r="F697" t="inlineStr">
         <is>
-          <t>2301762 000005/2025</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>DM-002/2024-A</t>
+          <t>DPEI-9446143</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>9410208</t>
+          <t>9446143</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
@@ -21232,19 +21240,19 @@
       <c r="E698" t="inlineStr"/>
       <c r="F698" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>2301601 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>DC-9479677/2025</t>
+          <t>DM-9474704/2025</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>9479677</t>
+          <t>9474704</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
@@ -21256,19 +21264,19 @@
       <c r="E699" t="inlineStr"/>
       <c r="F699" t="inlineStr">
         <is>
-          <t>2301520 000032/2025</t>
+          <t>2301762 000005/2025</t>
         </is>
       </c>
     </row>
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DM-9493202/2026</t>
+          <t>DM-002/2024-A</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>9493202</t>
+          <t>9410208</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
@@ -21280,19 +21288,19 @@
       <c r="E700" t="inlineStr"/>
       <c r="F700" t="inlineStr">
         <is>
-          <t>2301762 000025/2025</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>DM-9493137/2026</t>
+          <t>DC-9479677/2025</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>9493137</t>
+          <t>9479677</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
@@ -21304,19 +21312,19 @@
       <c r="E701" t="inlineStr"/>
       <c r="F701" t="inlineStr">
         <is>
-          <t>2301762 000022/2025</t>
+          <t>2301520 000032/2025</t>
         </is>
       </c>
     </row>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>DM-001/2024-B</t>
+          <t>DM-9493202/2026</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>9410177</t>
+          <t>9493202</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -21328,19 +21336,19 @@
       <c r="E702" t="inlineStr"/>
       <c r="F702" t="inlineStr">
         <is>
-          <t>2301762 000001/2024</t>
+          <t>2301762 000025/2025</t>
         </is>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>DC-011R/2024</t>
+          <t>DM-9493137/2026</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>9498942</t>
+          <t>9493137</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -21348,67 +21356,67 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr">
-        <is>
-          <t>-18.9494754</t>
-        </is>
-      </c>
-      <c r="E703" t="inlineStr">
-        <is>
-          <t>-46.9593239</t>
-        </is>
-      </c>
+      <c r="D703" t="inlineStr"/>
+      <c r="E703" t="inlineStr"/>
       <c r="F703" t="inlineStr">
         <is>
-          <t>2301520 000010/2026</t>
+          <t>2301762 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DM-001/2024-B</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>9393459</t>
+          <t>9410177</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D704" t="inlineStr"/>
       <c r="E704" t="inlineStr"/>
       <c r="F704" t="inlineStr">
         <is>
-          <t>2301601 000017/2022</t>
+          <t>2301762 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>DP-029/2023</t>
+          <t>DC-011R/2024</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>9393459</t>
+          <t>9498942</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Obra 5</t>
-        </is>
-      </c>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>-18.9494754</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>-46.9593239</t>
+        </is>
+      </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>2301601 000017/2022</t>
+          <t>2301520 000010/2026</t>
         </is>
       </c>
     </row>
@@ -21425,7 +21433,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D706" t="inlineStr"/>
@@ -21449,7 +21457,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 5</t>
         </is>
       </c>
       <c r="D707" t="inlineStr"/>
@@ -21473,7 +21481,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Obra 6</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D708" t="inlineStr"/>
@@ -21497,7 +21505,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D709" t="inlineStr"/>
@@ -21511,44 +21519,36 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9393459</t>
         </is>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D710" t="inlineStr">
-        <is>
-          <t>-16.1257215</t>
-        </is>
-      </c>
-      <c r="E710" t="inlineStr">
-        <is>
-          <t>-45.7410578</t>
-        </is>
-      </c>
+          <t>Obra 6</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
+      <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000017/2022</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>DC-003/2024</t>
+          <t>DP-029/2023</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>9417863</t>
+          <t>9393459</t>
         </is>
       </c>
       <c r="C711" t="inlineStr">
@@ -21556,31 +21556,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D711" t="inlineStr">
-        <is>
-          <t>-16.056339</t>
-        </is>
-      </c>
-      <c r="E711" t="inlineStr">
-        <is>
-          <t>-45.14616599999999</t>
-        </is>
-      </c>
+      <c r="D711" t="inlineStr"/>
+      <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr">
         <is>
-          <t>2301520 000001/2024</t>
+          <t>2301601 000017/2022</t>
         </is>
       </c>
     </row>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>9417858</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -21607,12 +21599,12 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>DC-002/2024</t>
+          <t>DC-003/2024</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>9417858</t>
+          <t>9417863</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -21639,12 +21631,12 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DPEI-002/2024</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>9414453</t>
+          <t>9417858</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -21654,29 +21646,29 @@
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>-16.7204079</t>
+          <t>-16.1257215</t>
         </is>
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>-43.8540743</t>
+          <t>-45.7410578</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>DPEI-006/2024</t>
+          <t>DC-002/2024</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>9416621</t>
+          <t>9417858</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -21686,29 +21678,29 @@
       </c>
       <c r="D715" t="inlineStr">
         <is>
-          <t>-21.5799309</t>
+          <t>-16.056339</t>
         </is>
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>-45.4427049</t>
+          <t>-45.14616599999999</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301520 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>DPEI-007/2024</t>
+          <t>DPEI-002/2024</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>9417534</t>
+          <t>9414453</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
@@ -21716,23 +21708,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-16.7204079</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-43.8540743</t>
+        </is>
+      </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>2301601 000006/2023</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DPEI-006/2024</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>9416621</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -21742,29 +21742,29 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>-21.8657357</t>
+          <t>-21.5799309</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>-43.01008239999999</t>
+          <t>-45.4427049</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>DPEI-007/2024</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>DPEI-030/2023</t>
+          <t>9417534</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -21772,19 +21772,11 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>-21.990801252388714</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>-42.90995722615383</t>
-        </is>
-      </c>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301601 000006/2023</t>
         </is>
       </c>
     </row>
@@ -21801,17 +21793,17 @@
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
         <is>
-          <t>-21.36383967660115</t>
+          <t>-21.8657357</t>
         </is>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>-42.67405889386136</t>
+          <t>-43.01008239999999</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
@@ -21833,17 +21825,17 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>-21.36590506590777</t>
+          <t>-21.990801252388714</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>-42.474979263671926</t>
+          <t>-42.90995722615383</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
@@ -21865,17 +21857,17 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>-21.416023487875883</t>
+          <t>-21.36383967660115</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>-42.815412025192636</t>
+          <t>-42.67405889386136</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
@@ -21897,17 +21889,17 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
         <is>
-          <t>-21.457172674928085</t>
+          <t>-21.36590506590777</t>
         </is>
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>-42.966439771920605</t>
+          <t>-42.474979263671926</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
@@ -21929,17 +21921,17 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>-21.196157236212304</t>
+          <t>-21.416023487875883</t>
         </is>
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>-42.62543945670461</t>
+          <t>-42.815412025192636</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
@@ -21961,17 +21953,17 @@
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>-21.151982349638054</t>
+          <t>-21.457172674928085</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>-42.79328856036735</t>
+          <t>-42.966439771920605</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
@@ -21983,76 +21975,76 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>DPEI-005/2024</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>9414322</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
         <is>
-          <t>-19.776208</t>
+          <t>-21.196157236212304</t>
         </is>
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>-43.948441</t>
+          <t>-42.62543945670461</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>DPEI-004/2024</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>9416600</t>
+          <t>DPEI-030/2023</t>
         </is>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 4</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
         <is>
-          <t>-20.7561451</t>
+          <t>-21.151982349638054</t>
         </is>
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>-42.8800278</t>
+          <t>-42.79328856036735</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>DM-011/2024</t>
+          <t>DPEI-005/2024</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9414322</t>
         </is>
       </c>
       <c r="C727" t="inlineStr">
@@ -22062,29 +22054,29 @@
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-19.776208</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>-44.943418</t>
+          <t>-43.948441</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DPEI-003/2024</t>
+          <t>DPEI-004/2024</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>9417600</t>
+          <t>9416600</t>
         </is>
       </c>
       <c r="C728" t="inlineStr">
@@ -22094,12 +22086,12 @@
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>-17.8517815</t>
+          <t>-20.7561451</t>
         </is>
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>-41.5076261</t>
+          <t>-42.8800278</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
@@ -22111,12 +22103,12 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>DM-022/2024</t>
+          <t>DM-011/2024</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C729" t="inlineStr">
@@ -22124,23 +22116,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F729" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>DM-020/2024</t>
+          <t>DPEI-003/2024</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9417600</t>
         </is>
       </c>
       <c r="C730" t="inlineStr">
@@ -22148,23 +22148,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr"/>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-17.8517815</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-41.5076261</t>
+        </is>
+      </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>DC-008/2024</t>
+          <t>DM-022/2024</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>9428115</t>
+          <t>9427765</t>
         </is>
       </c>
       <c r="C731" t="inlineStr">
@@ -22172,31 +22180,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr">
-        <is>
-          <t>-18.5985001</t>
-        </is>
-      </c>
-      <c r="E731" t="inlineStr">
-        <is>
-          <t>-45.35339499999999</t>
-        </is>
-      </c>
+      <c r="D731" t="inlineStr"/>
+      <c r="E731" t="inlineStr"/>
       <c r="F731" t="inlineStr">
         <is>
-          <t>2301520 000012/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>DC-008/2024</t>
+          <t>DM-020/2024</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>9428115</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C732" t="inlineStr">
@@ -22204,31 +22204,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D732" t="inlineStr">
-        <is>
-          <t>-18.43838275042916</t>
-        </is>
-      </c>
-      <c r="E732" t="inlineStr">
-        <is>
-          <t>-45.07210155240797</t>
-        </is>
-      </c>
+      <c r="D732" t="inlineStr"/>
+      <c r="E732" t="inlineStr"/>
       <c r="F732" t="inlineStr">
         <is>
-          <t>2301520 000012/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DM-9445782/2024</t>
+          <t>DC-008/2024</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>9445782</t>
+          <t>9428115</t>
         </is>
       </c>
       <c r="C733" t="inlineStr">
@@ -22238,29 +22230,29 @@
       </c>
       <c r="D733" t="inlineStr">
         <is>
-          <t>-22.4212558</t>
+          <t>-18.5985001</t>
         </is>
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>-45.47013339999999</t>
+          <t>-45.35339499999999</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>2301762 000114/2024</t>
+          <t>2301520 000012/2023</t>
         </is>
       </c>
     </row>
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>DM-9445784/2024</t>
+          <t>DC-008/2024</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>9445784</t>
+          <t>9428115</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -22270,29 +22262,29 @@
       </c>
       <c r="D734" t="inlineStr">
         <is>
-          <t>-22.431496</t>
+          <t>-18.43838275042916</t>
         </is>
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>-45.4633029</t>
+          <t>-45.07210155240797</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>2301762 000113/2024</t>
+          <t>2301520 000012/2023</t>
         </is>
       </c>
     </row>
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>DF/GTIC-9444079</t>
+          <t>DM-9445782/2024</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>9444079</t>
+          <t>9445782</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -22300,55 +22292,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D735" t="inlineStr"/>
-      <c r="E735" t="inlineStr"/>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-22.4212558</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-45.47013339999999</t>
+        </is>
+      </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>2301403 000100/2024</t>
+          <t>2301762 000114/2024</t>
         </is>
       </c>
     </row>
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>DC-9444080/2024</t>
+          <t>DM-9445784/2024</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>9444080</t>
+          <t>9445784</t>
         </is>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>-15.97197985837177</t>
+          <t>-22.431496</t>
         </is>
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>-44.90024660668347</t>
+          <t>-45.4633029</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>2301520 000017/2024</t>
+          <t>2301762 000113/2024</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>DC-9444080/2024</t>
+          <t>DF/GTIC-9444079</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>9444080</t>
+          <t>9444079</t>
         </is>
       </c>
       <c r="C737" t="inlineStr">
@@ -22356,63 +22356,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D737" t="inlineStr">
-        <is>
-          <t>-15.9662564146642</t>
-        </is>
-      </c>
-      <c r="E737" t="inlineStr">
-        <is>
-          <t>-44.90120778993473</t>
-        </is>
-      </c>
+      <c r="D737" t="inlineStr"/>
+      <c r="E737" t="inlineStr"/>
       <c r="F737" t="inlineStr">
         <is>
-          <t>2301520 000017/2024</t>
+          <t>2301403 000100/2024</t>
         </is>
       </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DM-019/2024</t>
+          <t>DC-9444080/2024</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>9424377</t>
+          <t>9444080</t>
         </is>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
         <is>
-          <t>-19.8162654081741</t>
+          <t>-15.97197985837177</t>
         </is>
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>-43.9479415297562</t>
+          <t>-44.90024660668347</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>2301762 000045/2023</t>
+          <t>2301520 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>DOV-004/2022-A</t>
+          <t>DC-9444080/2024</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>9344750</t>
+          <t>9444080</t>
         </is>
       </c>
       <c r="C739" t="inlineStr">
@@ -22420,23 +22412,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr"/>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-15.9662564146642</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-44.90120778993473</t>
+        </is>
+      </c>
       <c r="F739" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000017/2024</t>
         </is>
       </c>
     </row>
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>DC-9439921/2024</t>
+          <t>DM-019/2024</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>9439921</t>
+          <t>9424377</t>
         </is>
       </c>
       <c r="C740" t="inlineStr">
@@ -22446,29 +22446,29 @@
       </c>
       <c r="D740" t="inlineStr">
         <is>
-          <t>-22.60722055771159</t>
+          <t>-19.8162654081741</t>
         </is>
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>-46.04116272282801</t>
+          <t>-43.9479415297562</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>1301606 000001/2024</t>
+          <t>2301762 000045/2023</t>
         </is>
       </c>
     </row>
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>DC-9439921/2024</t>
+          <t>DOV-004/2022-A</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>9439921</t>
+          <t>9344750</t>
         </is>
       </c>
       <c r="C741" t="inlineStr">
@@ -22476,31 +22476,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D741" t="inlineStr">
-        <is>
-          <t>-22.58244462625664</t>
-        </is>
-      </c>
-      <c r="E741" t="inlineStr">
-        <is>
-          <t>-46.01200384097238</t>
-        </is>
-      </c>
+      <c r="D741" t="inlineStr"/>
+      <c r="E741" t="inlineStr"/>
       <c r="F741" t="inlineStr">
         <is>
-          <t>1301606 000001/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>DM-029/2023-A</t>
+          <t>DC-9439921/2024</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>9408476</t>
+          <t>9439921</t>
         </is>
       </c>
       <c r="C742" t="inlineStr">
@@ -22508,23 +22500,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
-      <c r="E742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-22.60722055771159</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-46.04116272282801</t>
+        </is>
+      </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>1301606 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>DM-030/2023-A</t>
+          <t>DC-9439921/2024</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>9408491</t>
+          <t>9439921</t>
         </is>
       </c>
       <c r="C743" t="inlineStr">
@@ -22534,29 +22534,29 @@
       </c>
       <c r="D743" t="inlineStr">
         <is>
-          <t>-19.5068923</t>
+          <t>-22.58244462625664</t>
         </is>
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>-42.6044222</t>
+          <t>-46.01200384097238</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>2301762 000027/2023</t>
+          <t>1301606 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>DC-9445592/2024</t>
+          <t>DM-029/2023-A</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>9445592</t>
+          <t>9408476</t>
         </is>
       </c>
       <c r="C744" t="inlineStr">
@@ -22564,31 +22564,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D744" t="inlineStr">
-        <is>
-          <t>-19.716466</t>
-        </is>
-      </c>
-      <c r="E744" t="inlineStr">
-        <is>
-          <t>-50.19527650000001</t>
-        </is>
-      </c>
+      <c r="D744" t="inlineStr"/>
+      <c r="E744" t="inlineStr"/>
       <c r="F744" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>AEST-009440673/2024</t>
+          <t>DM-030/2023-A</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>9440673</t>
+          <t>9408491</t>
         </is>
       </c>
       <c r="C745" t="inlineStr">
@@ -22596,23 +22588,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D745" t="inlineStr"/>
-      <c r="E745" t="inlineStr"/>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-19.5068923</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-42.6044222</t>
+        </is>
+      </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>2301931 000001/2024</t>
+          <t>2301762 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>DM-22.010/2019-E</t>
+          <t>DC-9445592/2024</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>9241241</t>
+          <t>9445592</t>
         </is>
       </c>
       <c r="C746" t="inlineStr">
@@ -22622,29 +22622,29 @@
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.716466</t>
         </is>
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-50.19527650000001</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>2301762 000019/2019</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>AEST-009440673/2024</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9440673</t>
         </is>
       </c>
       <c r="C747" t="inlineStr">
@@ -22652,31 +22652,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D747" t="inlineStr">
-        <is>
-          <t>-19.41249960000027</t>
-        </is>
-      </c>
-      <c r="E747" t="inlineStr">
-        <is>
-          <t>-44.20754999999095</t>
-        </is>
-      </c>
+      <c r="D747" t="inlineStr"/>
+      <c r="E747" t="inlineStr"/>
       <c r="F747" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301931 000001/2024</t>
         </is>
       </c>
     </row>
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>DC-9448965/2025</t>
+          <t>DM-22.010/2019-E</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>9448965</t>
+          <t>9241241</t>
         </is>
       </c>
       <c r="C748" t="inlineStr">
@@ -22686,17 +22678,17 @@
       </c>
       <c r="D748" t="inlineStr">
         <is>
-          <t>-19.4067426</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>-44.2266016</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>2301520 000025/2024</t>
+          <t>2301762 000019/2019</t>
         </is>
       </c>
     </row>
@@ -22718,12 +22710,12 @@
       </c>
       <c r="D749" t="inlineStr">
         <is>
-          <t>-19.4073712</t>
+          <t>-19.41249960000027</t>
         </is>
       </c>
       <c r="E749" t="inlineStr">
         <is>
-          <t>-44.20911359999999</t>
+          <t>-44.20754999999095</t>
         </is>
       </c>
       <c r="F749" t="inlineStr">
@@ -22735,44 +22727,44 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.4067426</t>
         </is>
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.2266016</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>DOV-001/2022-B</t>
+          <t>DC-9448965/2025</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>9344722</t>
+          <t>9448965</t>
         </is>
       </c>
       <c r="C751" t="inlineStr">
@@ -22782,53 +22774,61 @@
       </c>
       <c r="D751" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.4073712</t>
         </is>
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.20911359999999</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000025/2024</t>
         </is>
       </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>DM-9492723/2025</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>9492723</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>2301762 000024/2025</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>DM-9473163/2025</t>
+          <t>DOV-001/2022-B</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>9473163</t>
+          <t>9344722</t>
         </is>
       </c>
       <c r="C753" t="inlineStr">
@@ -22836,23 +22836,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr"/>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>DM-9471830/2025</t>
+          <t>DM-9492723/2025</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>9471830</t>
+          <t>9492723</t>
         </is>
       </c>
       <c r="C754" t="inlineStr">
@@ -22864,19 +22872,19 @@
       <c r="E754" t="inlineStr"/>
       <c r="F754" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301762 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>DM-9459013/2025</t>
+          <t>DM-9473163/2025</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>9459013</t>
+          <t>9473163</t>
         </is>
       </c>
       <c r="C755" t="inlineStr">
@@ -22888,19 +22896,19 @@
       <c r="E755" t="inlineStr"/>
       <c r="F755" t="inlineStr">
         <is>
-          <t>2301762 000020/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>AEST-9468704/2025</t>
+          <t>DM-9471830/2025</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>9468704</t>
+          <t>9471830</t>
         </is>
       </c>
       <c r="C756" t="inlineStr">
@@ -22912,19 +22920,19 @@
       <c r="E756" t="inlineStr"/>
       <c r="F756" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>DC-9478759/2025</t>
+          <t>DM-9459013/2025</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>9478759</t>
+          <t>9459013</t>
         </is>
       </c>
       <c r="C757" t="inlineStr">
@@ -22936,19 +22944,19 @@
       <c r="E757" t="inlineStr"/>
       <c r="F757" t="inlineStr">
         <is>
-          <t>2301520 000029/2025</t>
+          <t>2301762 000020/2024</t>
         </is>
       </c>
     </row>
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>DC-9447761/2025</t>
+          <t>AEST-9468704/2025</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>9447761</t>
+          <t>9468704</t>
         </is>
       </c>
       <c r="C758" t="inlineStr">
@@ -22956,31 +22964,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D758" t="inlineStr">
-        <is>
-          <t>-21.78317377768046</t>
-        </is>
-      </c>
-      <c r="E758" t="inlineStr">
-        <is>
-          <t>-45.83339382368384</t>
-        </is>
-      </c>
+      <c r="D758" t="inlineStr"/>
+      <c r="E758" t="inlineStr"/>
       <c r="F758" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>DC-9447760/2025</t>
+          <t>DC-9478759/2025</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>9447760</t>
+          <t>9478759</t>
         </is>
       </c>
       <c r="C759" t="inlineStr">
@@ -22988,31 +22988,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D759" t="inlineStr">
-        <is>
-          <t>-21.7907786</t>
-        </is>
-      </c>
-      <c r="E759" t="inlineStr">
-        <is>
-          <t>-45.7160543</t>
-        </is>
-      </c>
+      <c r="D759" t="inlineStr"/>
+      <c r="E759" t="inlineStr"/>
       <c r="F759" t="inlineStr">
         <is>
-          <t>2301520 000019/2024</t>
+          <t>2301520 000029/2025</t>
         </is>
       </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>DM-9471881/2025</t>
+          <t>DC-9447761/2025</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>9471881</t>
+          <t>9447761</t>
         </is>
       </c>
       <c r="C760" t="inlineStr">
@@ -23020,23 +23012,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D760" t="inlineStr"/>
-      <c r="E760" t="inlineStr"/>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-21.78317377768046</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-45.83339382368384</t>
+        </is>
+      </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DM-9471879/2025</t>
+          <t>DC-9447760/2025</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>9471879</t>
+          <t>9447760</t>
         </is>
       </c>
       <c r="C761" t="inlineStr">
@@ -23044,23 +23044,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>-21.7907786</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>-45.7160543</t>
+        </is>
+      </c>
       <c r="F761" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000019/2024</t>
         </is>
       </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>DC-9472756/2025</t>
+          <t>DM-9471881/2025</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>9472756</t>
+          <t>9471881</t>
         </is>
       </c>
       <c r="C762" t="inlineStr">
@@ -23072,19 +23080,19 @@
       <c r="E762" t="inlineStr"/>
       <c r="F762" t="inlineStr">
         <is>
-          <t>2301520 000002/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>DC-9473949/2025</t>
+          <t>DM-9471879/2025</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>9473949</t>
+          <t>9471879</t>
         </is>
       </c>
       <c r="C763" t="inlineStr">
@@ -23092,29 +23100,25 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D763" t="inlineStr">
-        <is>
-          <t>-20.32294571170053</t>
-        </is>
-      </c>
-      <c r="E763" t="inlineStr">
-        <is>
-          <t>-42.67292083028444</t>
-        </is>
-      </c>
+      <c r="D763" t="inlineStr"/>
+      <c r="E763" t="inlineStr"/>
       <c r="F763" t="inlineStr">
         <is>
-          <t>2301520 000018/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t xml:space="preserve"> AEST-9469794/2025</t>
-        </is>
-      </c>
-      <c r="B764" t="inlineStr"/>
+          <t>DC-9472756/2025</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>9472756</t>
+        </is>
+      </c>
       <c r="C764" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23122,17 +23126,21 @@
       </c>
       <c r="D764" t="inlineStr"/>
       <c r="E764" t="inlineStr"/>
-      <c r="F764" t="inlineStr"/>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2301520 000002/2025</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
+          <t>DC-9473949/2025</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>9473175</t>
+          <t>9473949</t>
         </is>
       </c>
       <c r="C765" t="inlineStr">
@@ -23142,53 +23150,45 @@
       </c>
       <c r="D765" t="inlineStr">
         <is>
-          <t>-14.77197791029356</t>
+          <t>-20.32294571170053</t>
         </is>
       </c>
       <c r="E765" t="inlineStr">
         <is>
-          <t>-43.93723839761794</t>
+          <t>-42.67292083028444</t>
         </is>
       </c>
       <c r="F765" t="inlineStr">
         <is>
-          <t>2301520 000016/2025</t>
+          <t>2301520 000018/2025</t>
         </is>
       </c>
     </row>
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>DC-009473175/2025</t>
-        </is>
-      </c>
-      <c r="B766" t="inlineStr">
-        <is>
-          <t>9473175</t>
-        </is>
-      </c>
+          <t xml:space="preserve"> AEST-9469794/2025</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr"/>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D766" t="inlineStr"/>
       <c r="E766" t="inlineStr"/>
-      <c r="F766" t="inlineStr">
-        <is>
-          <t>2301520 000016/2025</t>
-        </is>
-      </c>
+      <c r="F766" t="inlineStr"/>
     </row>
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>AMA-9447965/2025</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>9447965</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -23196,47 +23196,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>-14.77197791029356</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>-43.93723839761794</t>
+        </is>
+      </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>2301617 000004/2024</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>DPEI-9470151</t>
+          <t>DC-009473175/2025</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>9470151</t>
+          <t>9473175</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D768" t="inlineStr"/>
       <c r="E768" t="inlineStr"/>
       <c r="F768" t="inlineStr">
         <is>
-          <t>2301601 000003/2025</t>
+          <t>2301520 000016/2025</t>
         </is>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>DC-9439838/2024</t>
+          <t>AMA-9447965/2025</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>9439838</t>
+          <t>9447965</t>
         </is>
       </c>
       <c r="C769" t="inlineStr">
@@ -23244,31 +23252,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D769" t="inlineStr">
-        <is>
-          <t>-19.878035358432</t>
-        </is>
-      </c>
-      <c r="E769" t="inlineStr">
-        <is>
-          <t>-46.01755299600972</t>
-        </is>
-      </c>
+      <c r="D769" t="inlineStr"/>
+      <c r="E769" t="inlineStr"/>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2301520 000011/2024</t>
+          <t>2301617 000004/2024</t>
         </is>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>DC-9453556/2025</t>
+          <t>DPEI-9470151</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9470151</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
@@ -23276,31 +23276,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>-19.78342141078643</t>
-        </is>
-      </c>
-      <c r="E770" t="inlineStr">
-        <is>
-          <t>-43.951935887975836</t>
-        </is>
-      </c>
+      <c r="D770" t="inlineStr"/>
+      <c r="E770" t="inlineStr"/>
       <c r="F770" t="inlineStr">
         <is>
-          <t>2301520 000027/2023</t>
+          <t>2301601 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>DPEI-9447050</t>
+          <t>DC-9439838/2024</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>9447050</t>
+          <t>9439838</t>
         </is>
       </c>
       <c r="C771" t="inlineStr">
@@ -23308,23 +23300,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D771" t="inlineStr"/>
-      <c r="E771" t="inlineStr"/>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>-19.878035358432</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>-46.01755299600972</t>
+        </is>
+      </c>
       <c r="F771" t="inlineStr">
         <is>
-          <t>2301601 000003/2024</t>
+          <t>2301520 000011/2024</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>DC-9468321/2025</t>
+          <t>DC-9453556/2025</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>9468321</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
@@ -23334,29 +23334,29 @@
       </c>
       <c r="D772" t="inlineStr">
         <is>
-          <t>-21.822481</t>
+          <t>-19.78342141078643</t>
         </is>
       </c>
       <c r="E772" t="inlineStr">
         <is>
-          <t>-43.319474</t>
+          <t>-43.951935887975836</t>
         </is>
       </c>
       <c r="F772" t="inlineStr">
         <is>
-          <t>2301520 000007/2025</t>
+          <t>2301520 000027/2023</t>
         </is>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>DPEI-9447050</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9447050</t>
         </is>
       </c>
       <c r="C773" t="inlineStr">
@@ -23364,31 +23364,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr">
-        <is>
-          <t>-19.8898481</t>
-        </is>
-      </c>
-      <c r="E773" t="inlineStr">
-        <is>
-          <t>-49.3728646</t>
-        </is>
-      </c>
+      <c r="D773" t="inlineStr"/>
+      <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>2301601 000003/2024</t>
         </is>
       </c>
     </row>
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>DC-9470224/2025</t>
+          <t>DC-9468321/2025</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>9470224</t>
+          <t>9468321</t>
         </is>
       </c>
       <c r="C774" t="inlineStr">
@@ -23398,29 +23390,29 @@
       </c>
       <c r="D774" t="inlineStr">
         <is>
-          <t>-19.70009506319273</t>
+          <t>-21.822481</t>
         </is>
       </c>
       <c r="E774" t="inlineStr">
         <is>
-          <t>-49.31984772214537</t>
+          <t>-43.319474</t>
         </is>
       </c>
       <c r="F774" t="inlineStr">
         <is>
-          <t>1301606 000001/2025</t>
+          <t>2301520 000007/2025</t>
         </is>
       </c>
     </row>
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>DM-9471832/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>9471832</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="C775" t="inlineStr">
@@ -23428,23 +23420,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
-      <c r="E775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>-19.8898481</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>-49.3728646</t>
+        </is>
+      </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>DC-9471605/2025</t>
+          <t>DC-9470224/2025</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>9471605</t>
+          <t>9470224</t>
         </is>
       </c>
       <c r="C776" t="inlineStr">
@@ -23452,23 +23452,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D776" t="inlineStr"/>
-      <c r="E776" t="inlineStr"/>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>-19.70009506319273</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>-49.31984772214537</t>
+        </is>
+      </c>
       <c r="F776" t="inlineStr">
         <is>
-          <t>2301520 000011/2025</t>
+          <t>1301606 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>AEST-9441233/2024</t>
+          <t>DM-9471832/2025</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>9441233</t>
+          <t>9471832</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
@@ -23480,19 +23488,19 @@
       <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr">
         <is>
-          <t>2301931 000002/2024</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>AEST-9468573/2025</t>
+          <t>DC-9471605/2025</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>9468573</t>
+          <t>9471605</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
@@ -23504,19 +23512,19 @@
       <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr">
         <is>
-          <t>2301931 000002/2025</t>
+          <t>2301520 000011/2025</t>
         </is>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>AEST-9441233/2024</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9441233</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
@@ -23524,31 +23532,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D779" t="inlineStr">
-        <is>
-          <t>-16.060571</t>
-        </is>
-      </c>
-      <c r="E779" t="inlineStr">
-        <is>
-          <t>-45.14998800000001</t>
-        </is>
-      </c>
+      <c r="D779" t="inlineStr"/>
+      <c r="E779" t="inlineStr"/>
       <c r="F779" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301931 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>DC-9492718/2025</t>
+          <t>AEST-9468573/2025</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>9492718</t>
+          <t>9468573</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
@@ -23556,31 +23556,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D780" t="inlineStr">
-        <is>
-          <t>-16.12398555419337</t>
-        </is>
-      </c>
-      <c r="E780" t="inlineStr">
-        <is>
-          <t>-45.72443570435887</t>
-        </is>
-      </c>
+      <c r="D780" t="inlineStr"/>
+      <c r="E780" t="inlineStr"/>
       <c r="F780" t="inlineStr">
         <is>
-          <t>2301520 000022/2025</t>
+          <t>2301931 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
@@ -23590,29 +23582,29 @@
       </c>
       <c r="D781" t="inlineStr">
         <is>
-          <t>-18.58543851687659</t>
+          <t>-16.060571</t>
         </is>
       </c>
       <c r="E781" t="inlineStr">
         <is>
-          <t>-42.49387848441415</t>
+          <t>-45.14998800000001</t>
         </is>
       </c>
       <c r="F781" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>DC-9491012/2025</t>
+          <t>DC-9492718/2025</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>9491012</t>
+          <t>9492718</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
@@ -23622,29 +23614,29 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>-18.45181382097735</t>
+          <t>-16.12398555419337</t>
         </is>
       </c>
       <c r="E782" t="inlineStr">
         <is>
-          <t>-42.61418109121731</t>
+          <t>-45.72443570435887</t>
         </is>
       </c>
       <c r="F782" t="inlineStr">
         <is>
-          <t>2301520 000024/2025</t>
+          <t>2301520 000022/2025</t>
         </is>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>DC-9491013/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>9491013</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
@@ -23654,29 +23646,29 @@
       </c>
       <c r="D783" t="inlineStr">
         <is>
-          <t>-19.422927421098</t>
+          <t>-18.58543851687659</t>
         </is>
       </c>
       <c r="E783" t="inlineStr">
         <is>
-          <t>-44.54875745320115</t>
+          <t>-42.49387848441415</t>
         </is>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2301520 000028/2025</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-9491012/2025</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9491012</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
@@ -23686,29 +23678,29 @@
       </c>
       <c r="D784" t="inlineStr">
         <is>
-          <t>-18.3540804218777</t>
+          <t>-18.45181382097735</t>
         </is>
       </c>
       <c r="E784" t="inlineStr">
         <is>
-          <t>-48.23074551265237</t>
+          <t>-42.61418109121731</t>
         </is>
       </c>
       <c r="F784" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301520 000024/2025</t>
         </is>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>DC-9492083/2025</t>
+          <t>DC-9491013/2025</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>9492083</t>
+          <t>9491013</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
@@ -23718,29 +23710,29 @@
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>-18.5342387</t>
+          <t>-19.422927421098</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>-48.1962378</t>
+          <t>-44.54875745320115</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>2301520 000038/2025</t>
+          <t>2301520 000028/2025</t>
         </is>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>DM-9493180/2026</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>9493180</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
@@ -23748,23 +23740,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D786" t="inlineStr"/>
-      <c r="E786" t="inlineStr"/>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>-18.3540804218777</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>-48.23074551265237</t>
+        </is>
+      </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>DC-9492083/2025</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>9430925</t>
+          <t>9492083</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
@@ -23774,29 +23774,29 @@
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>-17.21201507063193</t>
+          <t>-18.5342387</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
         <is>
-          <t>-46.68787211434018</t>
+          <t>-48.1962378</t>
         </is>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>1301606 000003/2023</t>
+          <t>2301520 000038/2025</t>
         </is>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>DC-022/2023</t>
+          <t>DM-9493180/2026</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>9430925</t>
+          <t>9493180</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
@@ -23804,19 +23804,11 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D788" t="inlineStr">
-        <is>
-          <t>-17.10715545158019</t>
-        </is>
-      </c>
-      <c r="E788" t="inlineStr">
-        <is>
-          <t>-46.62095644997671</t>
-        </is>
-      </c>
+      <c r="D788" t="inlineStr"/>
+      <c r="E788" t="inlineStr"/>
       <c r="F788" t="inlineStr">
         <is>
-          <t>1301606 000003/2023</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
@@ -23833,17 +23825,17 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D789" t="inlineStr">
         <is>
-          <t>-17.10715545158019</t>
+          <t>-17.21201507063193</t>
         </is>
       </c>
       <c r="E789" t="inlineStr">
         <is>
-          <t>-46.62095644997671</t>
+          <t>-46.68787211434018</t>
         </is>
       </c>
       <c r="F789" t="inlineStr">
@@ -23865,17 +23857,17 @@
       </c>
       <c r="C790" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>-17.03493425248441</t>
+          <t>-17.10715545158019</t>
         </is>
       </c>
       <c r="E790" t="inlineStr">
         <is>
-          <t>-46.5886262006665</t>
+          <t>-46.62095644997671</t>
         </is>
       </c>
       <c r="F790" t="inlineStr">
@@ -23887,68 +23879,76 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>DOV-003/2022-A</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>9344739</t>
+          <t>9430925</t>
         </is>
       </c>
       <c r="C791" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D791" t="inlineStr"/>
-      <c r="E791" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>-17.10715545158019</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>-46.62095644997671</t>
+        </is>
+      </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>1301606 000003/2023</t>
         </is>
       </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-ANO 4</t>
+          <t>DC-022/2023</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9430925</t>
         </is>
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-17.03493425248441</t>
         </is>
       </c>
       <c r="E792" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-46.5886262006665</t>
         </is>
       </c>
       <c r="F792" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>1301606 000003/2023</t>
         </is>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>DC-9441306/2024</t>
+          <t>DOV-003/2022-A</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>9441306</t>
+          <t>9344739</t>
         </is>
       </c>
       <c r="C793" t="inlineStr">
@@ -23956,29 +23956,25 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D793" t="inlineStr">
-        <is>
-          <t>-15.600402</t>
-        </is>
-      </c>
-      <c r="E793" t="inlineStr">
-        <is>
-          <t>-42.543776</t>
-        </is>
-      </c>
+      <c r="D793" t="inlineStr"/>
+      <c r="E793" t="inlineStr"/>
       <c r="F793" t="inlineStr">
         <is>
-          <t>2301520 000012/2024</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t xml:space="preserve">DC-9441355/2024 </t>
-        </is>
-      </c>
-      <c r="B794" t="inlineStr"/>
+          <t>PRC-29.008/2017-ANO 4</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>9149606</t>
+        </is>
+      </c>
       <c r="C794" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -23986,25 +23982,29 @@
       </c>
       <c r="D794" t="inlineStr">
         <is>
-          <t>-17.82651719999999</t>
+          <t>-16.7203311</t>
         </is>
       </c>
       <c r="E794" t="inlineStr">
         <is>
-          <t>-41.506751</t>
-        </is>
-      </c>
-      <c r="F794" t="inlineStr"/>
+          <t>-43.8541147</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>2301901 000001/2017</t>
+        </is>
+      </c>
     </row>
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>DC-9445950/2024</t>
+          <t>DC-9441306/2024</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>9445950</t>
+          <t>9441306</t>
         </is>
       </c>
       <c r="C795" t="inlineStr">
@@ -24014,31 +24014,27 @@
       </c>
       <c r="D795" t="inlineStr">
         <is>
-          <t>-19.779781</t>
+          <t>-15.600402</t>
         </is>
       </c>
       <c r="E795" t="inlineStr">
         <is>
-          <t>-44.23890900000001</t>
+          <t>-42.543776</t>
         </is>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>2301520 002220/2024</t>
+          <t>2301520 000012/2024</t>
         </is>
       </c>
     </row>
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>DC-9445950/2024</t>
-        </is>
-      </c>
-      <c r="B796" t="inlineStr">
-        <is>
-          <t>9445950</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DC-9441355/2024 </t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr"/>
       <c r="C796" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -24046,29 +24042,25 @@
       </c>
       <c r="D796" t="inlineStr">
         <is>
-          <t>-19.83023</t>
+          <t>-17.82651719999999</t>
         </is>
       </c>
       <c r="E796" t="inlineStr">
         <is>
-          <t>-44.18012</t>
-        </is>
-      </c>
-      <c r="F796" t="inlineStr">
-        <is>
-          <t>2301520 002220/2024</t>
-        </is>
-      </c>
+          <t>-41.506751</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr"/>
     </row>
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>DC-9445591/2024</t>
+          <t>DC-9445950/2024</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>9445591</t>
+          <t>9445950</t>
         </is>
       </c>
       <c r="C797" t="inlineStr">
@@ -24078,12 +24070,12 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>-17.96127463110632</t>
+          <t>-19.779781</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>-46.42781545395799</t>
+          <t>-44.23890900000001</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
@@ -24095,12 +24087,12 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>DC-9445591/2024</t>
+          <t>DC-9445950/2024</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>9445591</t>
+          <t>9445950</t>
         </is>
       </c>
       <c r="C798" t="inlineStr">
@@ -24110,12 +24102,12 @@
       </c>
       <c r="D798" t="inlineStr">
         <is>
-          <t>-18.65274465135498</t>
+          <t>-19.83023</t>
         </is>
       </c>
       <c r="E798" t="inlineStr">
         <is>
-          <t>-46.59916240618842</t>
+          <t>-44.18012</t>
         </is>
       </c>
       <c r="F798" t="inlineStr">
@@ -24127,12 +24119,12 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>DM-9471880/2025</t>
+          <t>DC-9445591/2024</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>9471880</t>
+          <t>9445591</t>
         </is>
       </c>
       <c r="C799" t="inlineStr">
@@ -24140,23 +24132,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D799" t="inlineStr"/>
-      <c r="E799" t="inlineStr"/>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>-17.96127463110632</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>-46.42781545395799</t>
+        </is>
+      </c>
       <c r="F799" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>DM-9471834/2025</t>
+          <t>DC-9445591/2024</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>9471834</t>
+          <t>9445591</t>
         </is>
       </c>
       <c r="C800" t="inlineStr">
@@ -24164,23 +24164,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D800" t="inlineStr"/>
-      <c r="E800" t="inlineStr"/>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>-18.65274465135498</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>-46.59916240618842</t>
+        </is>
+      </c>
       <c r="F800" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301520 002220/2024</t>
         </is>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>DM-9473312/2025</t>
+          <t>DM-9471880/2025</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>9473312</t>
+          <t>9471880</t>
         </is>
       </c>
       <c r="C801" t="inlineStr">
@@ -24192,19 +24200,19 @@
       <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
-          <t>2301762 000004/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DM-9471834/2025</t>
         </is>
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9471834</t>
         </is>
       </c>
       <c r="C802" t="inlineStr">
@@ -24212,31 +24220,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D802" t="inlineStr">
-        <is>
-          <t>-18.694272</t>
-        </is>
-      </c>
-      <c r="E802" t="inlineStr">
-        <is>
-          <t>-43.434571</t>
-        </is>
-      </c>
+      <c r="D802" t="inlineStr"/>
+      <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>DC-9473951/2025</t>
+          <t>DM-9473312/2025</t>
         </is>
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>9473951</t>
+          <t>9473312</t>
         </is>
       </c>
       <c r="C803" t="inlineStr">
@@ -24244,31 +24244,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D803" t="inlineStr">
-        <is>
-          <t>-19.0126003</t>
-        </is>
-      </c>
-      <c r="E803" t="inlineStr">
-        <is>
-          <t>-43.4419084</t>
-        </is>
-      </c>
+      <c r="D803" t="inlineStr"/>
+      <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
-          <t>2301520 000010/2025</t>
+          <t>2301762 000004/2025</t>
         </is>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t>DOV-005/2022-B</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>9344755</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="C804" t="inlineStr">
@@ -24278,29 +24270,29 @@
       </c>
       <c r="D804" t="inlineStr">
         <is>
-          <t>-18.95121</t>
+          <t>-18.694272</t>
         </is>
       </c>
       <c r="E804" t="inlineStr">
         <is>
-          <t>-41.9528346</t>
+          <t>-43.434571</t>
         </is>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>2301901 000009/2021</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>DC-9493122/2026</t>
+          <t>DC-9473951/2025</t>
         </is>
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>9493122</t>
+          <t>9473951</t>
         </is>
       </c>
       <c r="C805" t="inlineStr">
@@ -24310,29 +24302,29 @@
       </c>
       <c r="D805" t="inlineStr">
         <is>
-          <t>-14.7566423</t>
+          <t>-19.0126003</t>
         </is>
       </c>
       <c r="E805" t="inlineStr">
         <is>
-          <t>-43.9321579</t>
+          <t>-43.4419084</t>
         </is>
       </c>
       <c r="F805" t="inlineStr">
         <is>
-          <t>2301520 000034/2025</t>
+          <t>2301520 000010/2025</t>
         </is>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t>DM-9471835/2025</t>
+          <t>DOV-005/2022-B</t>
         </is>
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>9471835</t>
+          <t>9344755</t>
         </is>
       </c>
       <c r="C806" t="inlineStr">
@@ -24340,23 +24332,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D806" t="inlineStr"/>
-      <c r="E806" t="inlineStr"/>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>-18.95121</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>-41.9528346</t>
+        </is>
+      </c>
       <c r="F806" t="inlineStr">
         <is>
-          <t>2301762 000001/2025</t>
+          <t>2301901 000009/2021</t>
         </is>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>DPEI-9478941/2025</t>
+          <t>DC-9493122/2026</t>
         </is>
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>9478941</t>
+          <t>9493122</t>
         </is>
       </c>
       <c r="C807" t="inlineStr">
@@ -24364,23 +24364,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>-14.7566423</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>-43.9321579</t>
+        </is>
+      </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>2301601 000005/2025</t>
+          <t>2301520 000034/2025</t>
         </is>
       </c>
     </row>
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>DOV-004/2021-A</t>
+          <t>DM-9471835/2025</t>
         </is>
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9471835</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
@@ -24388,31 +24396,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D808" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E808" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D808" t="inlineStr"/>
+      <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>DOV-003/2021-A</t>
+          <t>DPEI-9478941/2025</t>
         </is>
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9478941</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
@@ -24424,19 +24424,19 @@
       <c r="E809" t="inlineStr"/>
       <c r="F809" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301601 000005/2025</t>
         </is>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>DM-22.009/2020-D</t>
+          <t>DOV-004/2021-A</t>
         </is>
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>9245587</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
@@ -24446,29 +24446,29 @@
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>-20.405398</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
         <is>
-          <t>-42.886629</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F810" t="inlineStr">
         <is>
-          <t>2301762 000042/2019</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>DM-22.012/2020-D</t>
+          <t>DOV-003/2021-A</t>
         </is>
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>9245580</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
@@ -24476,31 +24476,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D811" t="inlineStr">
-        <is>
-          <t>-20.735033</t>
-        </is>
-      </c>
-      <c r="E811" t="inlineStr">
-        <is>
-          <t>-46.6045231</t>
-        </is>
-      </c>
+      <c r="D811" t="inlineStr"/>
+      <c r="E811" t="inlineStr"/>
       <c r="F811" t="inlineStr">
         <is>
-          <t>2301762 000043/2019</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>DM-009/2022-B</t>
+          <t>DM-22.009/2020-D</t>
         </is>
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>9327308</t>
+          <t>9245587</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
@@ -24510,29 +24502,29 @@
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>-20.350449</t>
+          <t>-20.405398</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
         <is>
-          <t>-41.9526169</t>
+          <t>-42.886629</t>
         </is>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>2301762 000087/2021</t>
+          <t>2301762 000042/2019</t>
         </is>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>DP-012/2023</t>
+          <t>DM-22.012/2020-D</t>
         </is>
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>9386092</t>
+          <t>9245580</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
@@ -24540,23 +24532,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D813" t="inlineStr"/>
-      <c r="E813" t="inlineStr"/>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>-20.735033</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>-46.6045231</t>
+        </is>
+      </c>
       <c r="F813" t="inlineStr">
         <is>
-          <t>2301601 000004/2023</t>
+          <t>2301762 000043/2019</t>
         </is>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>DOV-004/2021-B</t>
+          <t>DM-009/2022-B</t>
         </is>
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>9292043</t>
+          <t>9327308</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
@@ -24566,29 +24566,29 @@
       </c>
       <c r="D814" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-20.350449</t>
         </is>
       </c>
       <c r="E814" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-41.9526169</t>
         </is>
       </c>
       <c r="F814" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000087/2021</t>
         </is>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>DM-016/2024</t>
+          <t>DP-012/2023</t>
         </is>
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9386092</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
@@ -24600,19 +24600,19 @@
       <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301601 000004/2023</t>
         </is>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>DC-007/2024</t>
+          <t>DOV-004/2021-B</t>
         </is>
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>9424592</t>
+          <t>9292043</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
@@ -24620,23 +24620,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D816" t="inlineStr"/>
-      <c r="E816" t="inlineStr"/>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>2301520 000024/2023</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>DM-010/2024</t>
+          <t>DM-016/2024</t>
         </is>
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
@@ -24648,19 +24656,19 @@
       <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>DPEI-001/2024</t>
+          <t>DC-007/2024</t>
         </is>
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>9414354</t>
+          <t>9424592</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
@@ -24668,31 +24676,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D818" t="inlineStr">
-        <is>
-          <t>-18.5967086</t>
-        </is>
-      </c>
-      <c r="E818" t="inlineStr">
-        <is>
-          <t>-46.51810469999999</t>
-        </is>
-      </c>
+      <c r="D818" t="inlineStr"/>
+      <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr">
         <is>
-          <t>2301601 000002/2024</t>
+          <t>2301520 000024/2023</t>
         </is>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>DC-010/2024</t>
+          <t>DM-010/2024</t>
         </is>
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>9426807</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -24700,31 +24700,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D819" t="inlineStr">
-        <is>
-          <t>-20.39729542216063</t>
-        </is>
-      </c>
-      <c r="E819" t="inlineStr">
-        <is>
-          <t>-42.37959570001862</t>
-        </is>
-      </c>
+      <c r="D819" t="inlineStr"/>
+      <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr">
         <is>
-          <t>2301520 000029/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>DM-9453530</t>
+          <t>DPEI-001/2024</t>
         </is>
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>9453530</t>
+          <t>9414354</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -24732,23 +24724,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr"/>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>-18.5967086</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>-46.51810469999999</t>
+        </is>
+      </c>
       <c r="F820" t="inlineStr">
         <is>
-          <t>2301762 000021/2024</t>
+          <t>2301601 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>DOV-003/2021-B</t>
+          <t>DC-010/2024</t>
         </is>
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>9292042</t>
+          <t>9426807</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -24756,23 +24756,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D821" t="inlineStr"/>
-      <c r="E821" t="inlineStr"/>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>-20.39729542216063</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>-42.37959570001862</t>
+        </is>
+      </c>
       <c r="F821" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301520 000029/2023</t>
         </is>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>DM-018/2024</t>
+          <t>DM-9453530</t>
         </is>
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9453530</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -24784,19 +24792,19 @@
       <c r="E822" t="inlineStr"/>
       <c r="F822" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000021/2024</t>
         </is>
       </c>
     </row>
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>DM-014/2024</t>
+          <t>DOV-003/2021-B</t>
         </is>
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9292042</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -24804,31 +24812,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E823" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D823" t="inlineStr"/>
+      <c r="E823" t="inlineStr"/>
       <c r="F823" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>DG/AMA-009436677/2024</t>
+          <t>DM-018/2024</t>
         </is>
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>9436677</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -24840,19 +24840,19 @@
       <c r="E824" t="inlineStr"/>
       <c r="F824" t="inlineStr">
         <is>
-          <t>2301617 000002/2024</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>DOV-001/2021-B</t>
+          <t>DM-014/2024</t>
         </is>
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>9292037</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C825" t="inlineStr">
@@ -24862,29 +24862,29 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.8618029</t>
         </is>
       </c>
       <c r="E825" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-44.5829004</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>2301901 000008/2021</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>DOV-002/2021-B</t>
+          <t>DG/AMA-009436677/2024</t>
         </is>
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>DOV-002/2021-B</t>
+          <t>9436677</t>
         </is>
       </c>
       <c r="C826" t="inlineStr">
@@ -24896,19 +24896,19 @@
       <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301617 000002/2024</t>
         </is>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>DC-9495596/2026</t>
+          <t>DOV-001/2021-B</t>
         </is>
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>9495596</t>
+          <t>9292037</t>
         </is>
       </c>
       <c r="C827" t="inlineStr">
@@ -24918,29 +24918,29 @@
       </c>
       <c r="D827" t="inlineStr">
         <is>
-          <t>-19.96402458305301</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E827" t="inlineStr">
         <is>
-          <t>-44.72983589212661</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>2301520 000030/2025</t>
+          <t>2301901 000008/2021</t>
         </is>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>DO-9493205/2026-L4</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>9493205</t>
+          <t>DOV-002/2021-B</t>
         </is>
       </c>
       <c r="C828" t="inlineStr">
@@ -24948,31 +24948,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D828" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E828" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D828" t="inlineStr"/>
+      <c r="E828" t="inlineStr"/>
       <c r="F828" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>Não Disponível</t>
         </is>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>D0-009482032/2025-L6</t>
+          <t>DC-9495596/2026</t>
         </is>
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>9482032</t>
+          <t>9495596</t>
         </is>
       </c>
       <c r="C829" t="inlineStr">
@@ -24982,29 +24974,29 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.96402458305301</t>
         </is>
       </c>
       <c r="E829" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.72983589212661</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>DO-9481987/2025-L7</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>9481987</t>
+          <t>9493205</t>
         </is>
       </c>
       <c r="C830" t="inlineStr">
@@ -25031,12 +25023,12 @@
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DO-009482055/2025-L5</t>
+          <t>DO-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>9482055</t>
+          <t>9482032</t>
         </is>
       </c>
       <c r="C831" t="inlineStr">
@@ -25063,12 +25055,12 @@
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DM-005/2024-A</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>9414460</t>
+          <t>9481987</t>
         </is>
       </c>
       <c r="C832" t="inlineStr">
@@ -25078,29 +25070,29 @@
       </c>
       <c r="D832" t="inlineStr">
         <is>
-          <t>-19.7469167</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E832" t="inlineStr">
         <is>
-          <t>-47.9483714</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F832" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DM-9497685/2026</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>9497685</t>
+          <t>9482055</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
@@ -25108,75 +25100,75 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D833" t="inlineStr"/>
-      <c r="E833" t="inlineStr"/>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F833" t="inlineStr">
         <is>
-          <t>2301762 000023/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-005/2024-A</t>
         </is>
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9414460</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-19.7469167</t>
         </is>
       </c>
       <c r="E834" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-47.9483714</t>
         </is>
       </c>
       <c r="F834" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DC-9507997/2026</t>
+          <t>DM-9497685/2026</t>
         </is>
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>9507997</t>
+          <t>9497685</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D835" t="inlineStr">
-        <is>
-          <t>-17.10715545158923</t>
-        </is>
-      </c>
-      <c r="E835" t="inlineStr">
-        <is>
-          <t>-46.62095644999281</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr"/>
+      <c r="E835" t="inlineStr"/>
       <c r="F835" t="inlineStr">
         <is>
-          <t>1301606 000002/2026</t>
+          <t>2301762 000023/2025</t>
         </is>
       </c>
     </row>
@@ -25198,12 +25190,12 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -25230,12 +25222,12 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25257,17 +25249,17 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25289,17 +25281,17 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25326,12 +25318,12 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25358,12 +25350,12 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25375,12 +25367,12 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>9501894</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C842" t="inlineStr">
@@ -25388,23 +25380,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>2301520 000042/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C843" t="inlineStr">
@@ -25414,29 +25414,29 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
+          <t>DC-9501894/2026</t>
         </is>
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>9518766</t>
+          <t>9501894</t>
         </is>
       </c>
       <c r="C844" t="inlineStr">
@@ -25444,31 +25444,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D844" t="inlineStr">
-        <is>
-          <t>-15.5007309</t>
-        </is>
-      </c>
-      <c r="E844" t="inlineStr">
-        <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
+      <c r="D844" t="inlineStr"/>
+      <c r="E844" t="inlineStr"/>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2301520 000047/2025</t>
+          <t>2301520 000042/2025</t>
         </is>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C845" t="inlineStr">
@@ -25478,29 +25470,29 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-15.483562</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.39677500000001</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C846" t="inlineStr">
@@ -25510,29 +25502,29 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-15.5007309</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-44.7624674</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>2301520 000047/2025</t>
         </is>
       </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25559,12 +25551,12 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25572,23 +25564,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr"/>
-      <c r="E848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25596,11 +25596,19 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D849" t="inlineStr"/>
-      <c r="E849" t="inlineStr"/>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
@@ -25655,12 +25663,12 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C852" t="inlineStr">
@@ -25668,83 +25676,67 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr">
-        <is>
-          <t>-21.1994491</t>
-        </is>
-      </c>
-      <c r="E852" t="inlineStr">
-        <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
+      <c r="D852" t="inlineStr"/>
+      <c r="E852" t="inlineStr"/>
       <c r="F852" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D853" t="inlineStr">
-        <is>
-          <t>-21.27464910003665</t>
-        </is>
-      </c>
-      <c r="E853" t="inlineStr">
-        <is>
-          <t>-42.91331545001727</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr"/>
+      <c r="E853" t="inlineStr"/>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>9515457</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
+          <t>-43.7852868</t>
         </is>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2301520 000005/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25753,17 @@
       </c>
       <c r="C855" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-21.27464910003665</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
+          <t>-42.91331545001727</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
@@ -25783,84 +25775,108 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9519020</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.6107675</t>
+          <t>-21.23264738347681</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-42.64891799999999</t>
+          <t>-43.43361939286979</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301520 000027/2026</t>
+          <t>2301520 000005/2026</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B857" t="inlineStr"/>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>9515457</t>
+        </is>
+      </c>
       <c r="C857" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
-      <c r="F857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>-21.23528484003703</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2301520 000005/2026</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-19.6107675</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-42.64891799999999</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000027/2026</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25868,55 +25884,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301520 000011/2026</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D860" t="inlineStr"/>
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25924,23 +25932,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr"/>
-      <c r="E861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C862" t="inlineStr">
@@ -25948,31 +25964,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D862" t="inlineStr">
-        <is>
-          <t>-17.335013</t>
-        </is>
-      </c>
-      <c r="E862" t="inlineStr">
-        <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
+      <c r="D862" t="inlineStr"/>
+      <c r="E862" t="inlineStr"/>
       <c r="F862" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C863" t="inlineStr">
@@ -25991,12 +25999,12 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
@@ -26004,8 +26012,16 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr"/>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F864" t="inlineStr">
         <is>
           <t>2301762 000036/2023</t>
@@ -26015,10 +26031,14 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr"/>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
       <c r="C865" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26026,17 +26046,21 @@
       </c>
       <c r="D865" t="inlineStr"/>
       <c r="E865" t="inlineStr"/>
-      <c r="F865" t="inlineStr"/>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>9500304</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C866" t="inlineStr">
@@ -26048,51 +26072,35 @@
       <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr">
         <is>
-          <t>2301762 000027/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr">
-        <is>
-          <t>9512043</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr"/>
       <c r="C867" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
-      <c r="F867" t="inlineStr">
-        <is>
-          <t>2301762 000004/2026</t>
-        </is>
-      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
+      <c r="F867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DM-9500304/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9500304</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
@@ -26100,31 +26108,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E868" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301762 000027/2025</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
+          <t>DM-9512043/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9512044</t>
+          <t>9512043</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -26132,55 +26132,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>2301762 000001/2026</t>
+          <t>2301762 000004/2026</t>
         </is>
       </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>-19.928208</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>-43.983328</t>
+          <t>-50.219328</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26188,23 +26196,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-19.0966327</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-46.67356590000001</t>
+        </is>
+      </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>DC-9519295/2026</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9519295</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26214,29 +26230,29 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>-19.8618029</t>
+          <t>-19.071165</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>-44.5829004</t>
+          <t>-46.794155</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000023/2026</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26246,29 +26262,29 @@
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>-16.7203311</t>
+          <t>-20.011794067707264</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
         <is>
-          <t>-43.8541147</t>
+          <t>-44.21840097426832</t>
         </is>
       </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9518140/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9518140</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26278,29 +26294,29 @@
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-20.051632324197044</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-44.19399735422576</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301520 000007/2026</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>DM-9512044/2026</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9512044</t>
         </is>
       </c>
       <c r="C875" t="inlineStr">
@@ -26308,55 +26324,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D875" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E875" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D875" t="inlineStr"/>
+      <c r="E875" t="inlineStr"/>
       <c r="F875" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301762 000001/2026</t>
         </is>
       </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D876" t="inlineStr"/>
-      <c r="E876" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
       <c r="F876" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
@@ -26368,19 +26384,19 @@
       <c r="E877" t="inlineStr"/>
       <c r="F877" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26388,23 +26404,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr"/>
-      <c r="E878" t="inlineStr"/>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C879" t="inlineStr">
@@ -26412,55 +26436,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D880" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-22.6434039</t>
         </is>
       </c>
       <c r="E880" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
+          <t>-46.3795013</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C881" t="inlineStr">
@@ -26470,61 +26502,53 @@
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>-16.11921421383736</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
         <is>
-          <t>-45.58712745575681</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E882" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
       <c r="F882" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C883" t="inlineStr">
@@ -26536,19 +26560,19 @@
       <c r="E883" t="inlineStr"/>
       <c r="F883" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
@@ -26560,19 +26584,19 @@
       <c r="E884" t="inlineStr"/>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26584,43 +26608,51 @@
       <c r="E885" t="inlineStr"/>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D886" t="inlineStr"/>
-      <c r="E886" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26628,55 +26660,63 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr"/>
-      <c r="E887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9501601</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 3</t>
         </is>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>-17.8518635</t>
+          <t>-16.12119845072</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
         <is>
-          <t>-41.5076927</t>
+          <t>-45.6488268407393</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000037/2025</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>DC-9493529/2026</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9493529</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26684,55 +26724,47 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E889" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000036/2025</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-012/2024-A</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9422079</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr"/>
       <c r="F890" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-9502116/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9502116</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -26744,67 +26776,67 @@
       <c r="E891" t="inlineStr"/>
       <c r="F891" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000026/2025</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-018/2024-A</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424304</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr"/>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
+          <t>DM-016/2024-A</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9511902</t>
+          <t>9424337</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr"/>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2301520 000001/2026</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>9519034</t>
+          <t>9427674</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
@@ -26812,41 +26844,201 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D894" t="inlineStr"/>
-      <c r="E894" t="inlineStr"/>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
       <c r="F894" t="inlineStr">
         <is>
-          <t>2301762 000028/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr"/>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2301520 000001/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>2301762 000028/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B895" t="inlineStr">
+      <c r="B901" t="inlineStr">
         <is>
           <t>9519017</t>
         </is>
       </c>
-      <c r="C895" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D895" t="inlineStr">
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
         <is>
           <t>-18.46005275010656</t>
         </is>
       </c>
-      <c r="E895" t="inlineStr">
+      <c r="E901" t="inlineStr">
         <is>
           <t>-48.18218127247928</t>
         </is>
       </c>
-      <c r="F895" t="inlineStr">
+      <c r="F901" t="inlineStr">
         <is>
           <t>2301520 000017/2026</t>
         </is>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F897"/>
+  <dimension ref="A1:F909"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25190,12 +25190,12 @@
       </c>
       <c r="D836" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E836" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F836" t="inlineStr">
@@ -25222,12 +25222,12 @@
       </c>
       <c r="D837" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E837" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F837" t="inlineStr">
@@ -25249,17 +25249,17 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25281,17 +25281,17 @@
       </c>
       <c r="C839" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25313,17 +25313,17 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25345,17 +25345,17 @@
       </c>
       <c r="C841" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25367,26 +25367,46 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B842" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C842" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
-      <c r="F842" t="inlineStr"/>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>-17.21201508102213</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B843" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C843" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25394,23 +25414,31 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
-        </is>
-      </c>
-      <c r="F843" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B844" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C844" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25418,23 +25446,31 @@
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
-      <c r="F844" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B845" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C845" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25442,23 +25478,31 @@
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-19.2091689</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-44.24819679999999</t>
-        </is>
-      </c>
-      <c r="F845" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B846" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C846" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25466,25 +25510,29 @@
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-19.347297668442856</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-44.17816254149293</t>
-        </is>
-      </c>
-      <c r="F846" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C847" t="inlineStr">
@@ -25494,29 +25542,29 @@
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C848" t="inlineStr">
@@ -25526,29 +25574,29 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
@@ -25558,31 +25606,27 @@
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B850" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr"/>
       <c r="C850" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25590,40 +25634,36 @@
       </c>
       <c r="D850" t="inlineStr"/>
       <c r="E850" t="inlineStr"/>
-      <c r="F850" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="F850" t="inlineStr"/>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B851" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr"/>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
-      <c r="F851" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>-15.483562</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>-44.39677500000001</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr"/>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B852" t="inlineStr"/>
@@ -25634,12 +25674,12 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-15.5007309</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
+          <t>-44.7624674</t>
         </is>
       </c>
       <c r="F852" t="inlineStr"/>
@@ -25647,23 +25687,23 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B853" t="inlineStr"/>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-19.2091689</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
+          <t>-44.24819679999999</t>
         </is>
       </c>
       <c r="F853" t="inlineStr"/>
@@ -25671,23 +25711,23 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B854" t="inlineStr"/>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-19.347297668442856</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
+          <t>-44.17816254149293</t>
         </is>
       </c>
       <c r="F854" t="inlineStr"/>
@@ -25695,10 +25735,14 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B855" t="inlineStr"/>
+          <t>DO-009482014/2025-L1</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>9482014</t>
+        </is>
+      </c>
       <c r="C855" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25706,23 +25750,31 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
-      <c r="F855" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
-        </is>
-      </c>
-      <c r="B856" t="inlineStr"/>
+          <t>DO-009482046/2025-L2</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>9482046</t>
+        </is>
+      </c>
       <c r="C856" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25730,65 +25782,85 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.6107675</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-42.64891799999999</t>
-        </is>
-      </c>
-      <c r="F856" t="inlineStr"/>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B857" t="inlineStr"/>
+          <t>DO-009482017/2025-L3</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>9482017</t>
+        </is>
+      </c>
       <c r="C857" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
-      <c r="F857" t="inlineStr"/>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>2301901 000001/2025</t>
+        </is>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr"/>
       <c r="F858" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25796,31 +25868,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr">
-        <is>
-          <t>-19.78548575576804</t>
-        </is>
-      </c>
-      <c r="E859" t="inlineStr">
-        <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
+      <c r="D859" t="inlineStr"/>
+      <c r="E859" t="inlineStr"/>
       <c r="F859" t="inlineStr">
         <is>
-          <t>1301606 000002/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25832,19 +25896,19 @@
       <c r="E860" t="inlineStr"/>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301520 000041/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25856,21 +25920,17 @@
       <c r="E861" t="inlineStr"/>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
-        </is>
-      </c>
-      <c r="B862" t="inlineStr">
-        <is>
-          <t>9421657</t>
-        </is>
-      </c>
+          <t>DM-007/2024-A</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr"/>
       <c r="C862" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25878,72 +25938,68 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-21.1994491</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>-44.943418</t>
-        </is>
-      </c>
-      <c r="F862" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>-43.7852868</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr"/>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
-        </is>
-      </c>
-      <c r="B863" t="inlineStr">
-        <is>
-          <t>9422078</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr"/>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
-      <c r="F863" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>-21.27464910003665</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>-42.91331545001727</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr"/>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
-        </is>
-      </c>
-      <c r="B864" t="inlineStr">
-        <is>
-          <t>9418600</t>
-        </is>
-      </c>
+          <t>DC-9515457/2026</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr"/>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr"/>
-      <c r="F864" t="inlineStr">
-        <is>
-          <t>2301762 000036/2023</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>-21.23264738347681</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr"/>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B865" t="inlineStr"/>
@@ -25952,14 +26008,22 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D865" t="inlineStr"/>
-      <c r="E865" t="inlineStr"/>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>-21.23528484003703</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
       <c r="F865" t="inlineStr"/>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B866" t="inlineStr"/>
@@ -25968,14 +26032,22 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr"/>
-      <c r="E866" t="inlineStr"/>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>-19.6107675</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>-42.64891799999999</t>
+        </is>
+      </c>
       <c r="F866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B867" t="inlineStr"/>
@@ -25984,57 +26056,45 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E867" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D867" t="inlineStr"/>
+      <c r="E867" t="inlineStr"/>
       <c r="F867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D868" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E868" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr"/>
+      <c r="E868" t="inlineStr"/>
       <c r="F868" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
-        </is>
-      </c>
-      <c r="B869" t="inlineStr"/>
+          <t>DC-9496643/2026</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>9496643</t>
+        </is>
+      </c>
       <c r="C869" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26042,71 +26102,79 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>-19.0966327</t>
+          <t>-19.78548575576804</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>-46.67356590000001</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr"/>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>1301606 000002/2025</t>
+        </is>
+      </c>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
-        </is>
-      </c>
-      <c r="B870" t="inlineStr"/>
+          <t>DC-9498666/2026</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>9453556</t>
+        </is>
+      </c>
       <c r="C870" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr">
-        <is>
-          <t>-19.071165</t>
-        </is>
-      </c>
-      <c r="E870" t="inlineStr">
-        <is>
-          <t>-46.794155</t>
-        </is>
-      </c>
-      <c r="F870" t="inlineStr"/>
+      <c r="D870" t="inlineStr"/>
+      <c r="E870" t="inlineStr"/>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>2301520 000041/2025</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
-      <c r="B871" t="inlineStr"/>
+          <t>DM-008/2024-A</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>9422064</t>
+        </is>
+      </c>
       <c r="C871" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr">
-        <is>
-          <t>-20.011794067707264</t>
-        </is>
-      </c>
-      <c r="E871" t="inlineStr">
-        <is>
-          <t>-44.21840097426832</t>
-        </is>
-      </c>
-      <c r="F871" t="inlineStr"/>
+      <c r="D871" t="inlineStr"/>
+      <c r="E871" t="inlineStr"/>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
-      <c r="B872" t="inlineStr"/>
+          <t>DM-011/2024-A</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>9421657</t>
+        </is>
+      </c>
       <c r="C872" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26114,23 +26182,31 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>-20.051632324197044</t>
+          <t>-17.335013</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>-44.19399735422576</t>
-        </is>
-      </c>
-      <c r="F872" t="inlineStr"/>
+          <t>-44.943418</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B873" t="inlineStr"/>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>9422078</t>
+        </is>
+      </c>
       <c r="C873" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26138,51 +26214,43 @@
       </c>
       <c r="D873" t="inlineStr"/>
       <c r="E873" t="inlineStr"/>
-      <c r="F873" t="inlineStr"/>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D874" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E874" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr"/>
+      <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
-        </is>
-      </c>
-      <c r="B875" t="inlineStr">
-        <is>
-          <t>9424449</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr"/>
       <c r="C875" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26190,55 +26258,31 @@
       </c>
       <c r="D875" t="inlineStr"/>
       <c r="E875" t="inlineStr"/>
-      <c r="F875" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
+      <c r="F875" t="inlineStr"/>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr">
-        <is>
-          <t>9424302</t>
-        </is>
-      </c>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr"/>
       <c r="C876" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D876" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E876" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
-      <c r="F876" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
+      <c r="D876" t="inlineStr"/>
+      <c r="E876" t="inlineStr"/>
+      <c r="F876" t="inlineStr"/>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr">
-        <is>
-          <t>9149606</t>
-        </is>
-      </c>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr"/>
       <c r="C877" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26254,21 +26298,17 @@
           <t>-43.8541147</t>
         </is>
       </c>
-      <c r="F877" t="inlineStr">
-        <is>
-          <t>2301901 000001/2017</t>
-        </is>
-      </c>
+      <c r="F877" t="inlineStr"/>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9497471</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26278,31 +26318,27 @@
       </c>
       <c r="D878" t="inlineStr">
         <is>
-          <t>-22.6434039</t>
+          <t>-19.747173</t>
         </is>
       </c>
       <c r="E878" t="inlineStr">
         <is>
-          <t>-46.3795013</t>
+          <t>-50.219328</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>1301606 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr">
-        <is>
-          <t>9504058</t>
-        </is>
-      </c>
+          <t>DC-9519295/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr"/>
       <c r="C879" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26310,173 +26346,145 @@
       </c>
       <c r="D879" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-19.0966327</t>
         </is>
       </c>
       <c r="E879" t="inlineStr">
         <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr">
-        <is>
-          <t>2301762 000030/2025</t>
-        </is>
-      </c>
+          <t>-46.67356590000001</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr"/>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DC-9519295/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr"/>
       <c r="C880" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
-      <c r="F880" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>-19.071165</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>-46.794155</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr"/>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr">
-        <is>
-          <t>9499286</t>
-        </is>
-      </c>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr"/>
       <c r="C881" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>-20.011794067707264</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>-44.21840097426832</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr"/>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr"/>
       <c r="C882" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-20.051632324197044</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+          <t>-44.19399735422576</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr"/>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
-        </is>
-      </c>
-      <c r="B883" t="inlineStr">
-        <is>
-          <t>9501601</t>
-        </is>
-      </c>
+          <t>DM-9512044/2026</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr"/>
       <c r="C883" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D883" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E883" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
-      <c r="F883" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+      <c r="D883" t="inlineStr"/>
+      <c r="E883" t="inlineStr"/>
+      <c r="F883" t="inlineStr"/>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DO-001/2021- C</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9275590</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D884" t="inlineStr">
         <is>
-          <t>-16.12119845072</t>
+          <t>-19.928208</t>
         </is>
       </c>
       <c r="E884" t="inlineStr">
         <is>
-          <t>-45.6488268407393</t>
+          <t>-43.983328</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>2301901 000003/2021</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9424449</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26488,19 +26496,19 @@
       <c r="E885" t="inlineStr"/>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9424302</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26508,23 +26516,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr"/>
-      <c r="E886" t="inlineStr"/>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
       <c r="F886" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301762 000051/2023</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>PRC-29.008/2017-E</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9149606</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26532,23 +26548,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr"/>
-      <c r="E887" t="inlineStr"/>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301901 000001/2017</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9505062</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -26556,23 +26580,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301520 000044/2025</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9504058</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26580,23 +26612,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000030/2025</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -26604,31 +26644,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E890" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D890" t="inlineStr"/>
+      <c r="E890" t="inlineStr"/>
       <c r="F890" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9427765</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
@@ -26636,45 +26668,49 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D891" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E891" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
+      <c r="D891" t="inlineStr"/>
+      <c r="E891" t="inlineStr"/>
       <c r="F891" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B892" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr"/>
-      <c r="F892" t="inlineStr"/>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B893" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C893" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26682,79 +26718,395 @@
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr"/>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B894" t="inlineStr"/>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D894" t="inlineStr"/>
-      <c r="E894" t="inlineStr"/>
-      <c r="F894" t="inlineStr"/>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B895" t="inlineStr"/>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D895" t="inlineStr"/>
-      <c r="E895" t="inlineStr"/>
-      <c r="F895" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
-      <c r="B896" t="inlineStr"/>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D896" t="inlineStr"/>
-      <c r="E896" t="inlineStr"/>
-      <c r="F896" t="inlineStr"/>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr"/>
+      <c r="E897" t="inlineStr"/>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>2301520 000036/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>9422079</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr"/>
+      <c r="E898" t="inlineStr"/>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr"/>
+      <c r="E899" t="inlineStr"/>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>9424304</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr"/>
+      <c r="E900" t="inlineStr"/>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr"/>
+      <c r="E901" t="inlineStr"/>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr"/>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr"/>
+      <c r="E904" t="inlineStr"/>
+      <c r="F904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr"/>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr"/>
+      <c r="E905" t="inlineStr"/>
+      <c r="F905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr"/>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr"/>
+      <c r="E906" t="inlineStr"/>
+      <c r="F906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr"/>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr"/>
+      <c r="E907" t="inlineStr"/>
+      <c r="F907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr"/>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr"/>
+      <c r="E908" t="inlineStr"/>
+      <c r="F908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B897" t="inlineStr"/>
-      <c r="C897" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D897" t="inlineStr">
+      <c r="B909" t="inlineStr"/>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
         <is>
           <t>-18.46005275010656</t>
         </is>
       </c>
-      <c r="E897" t="inlineStr">
+      <c r="E909" t="inlineStr">
         <is>
           <t>-48.18218127247928</t>
         </is>
       </c>
-      <c r="F897" t="inlineStr"/>
+      <c r="F909" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/upload/coordenadas.xlsx
+++ b/upload/coordenadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F909"/>
+  <dimension ref="A1:F949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24970,7 +24970,11 @@
           <t>DO-009482032/2025-L6</t>
         </is>
       </c>
-      <c r="B829" t="inlineStr"/>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>9482032</t>
+        </is>
+      </c>
       <c r="C829" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25254,12 +25258,12 @@
       </c>
       <c r="D838" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E838" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F838" t="inlineStr">
@@ -25286,12 +25290,12 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E839" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F839" t="inlineStr">
@@ -25318,12 +25322,12 @@
       </c>
       <c r="D840" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E840" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F840" t="inlineStr">
@@ -25350,12 +25354,12 @@
       </c>
       <c r="D841" t="inlineStr">
         <is>
-          <t>-17.03493425248546</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E841" t="inlineStr">
         <is>
-          <t>-46.58862620066699</t>
+          <t>-46.62095644999281</t>
         </is>
       </c>
       <c r="F841" t="inlineStr">
@@ -25377,17 +25381,17 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D842" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E842" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F842" t="inlineStr">
@@ -25409,17 +25413,17 @@
       </c>
       <c r="C843" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E843" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F843" t="inlineStr">
@@ -25441,17 +25445,17 @@
       </c>
       <c r="C844" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D844" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E844" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F844" t="inlineStr">
@@ -25473,17 +25477,17 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D845" t="inlineStr">
         <is>
-          <t>-17.21201508102213</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E845" t="inlineStr">
         <is>
-          <t>-46.687872082284</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F845" t="inlineStr">
@@ -25505,17 +25509,17 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D846" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E846" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F846" t="inlineStr">
@@ -25537,17 +25541,17 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D847" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E847" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F847" t="inlineStr">
@@ -25569,17 +25573,17 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F848" t="inlineStr">
@@ -25601,17 +25605,17 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Obra 1</t>
+          <t>Obra 2</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
         <is>
-          <t>-17.10715545158923</t>
+          <t>-17.03493425248546</t>
         </is>
       </c>
       <c r="E849" t="inlineStr">
         <is>
-          <t>-46.62095644999281</t>
+          <t>-46.58862620066699</t>
         </is>
       </c>
       <c r="F849" t="inlineStr">
@@ -25623,26 +25627,46 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>DC-9501894/2026</t>
-        </is>
-      </c>
-      <c r="B850" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C850" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D850" t="inlineStr"/>
-      <c r="E850" t="inlineStr"/>
-      <c r="F850" t="inlineStr"/>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>-17.21201508102213</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B851" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C851" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25650,23 +25674,31 @@
       </c>
       <c r="D851" t="inlineStr">
         <is>
-          <t>-15.483562</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E851" t="inlineStr">
         <is>
-          <t>-44.39677500000001</t>
-        </is>
-      </c>
-      <c r="F851" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>DC-9518766/2026</t>
-        </is>
-      </c>
-      <c r="B852" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C852" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25674,23 +25706,31 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>-15.5007309</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">
         <is>
-          <t>-44.7624674</t>
-        </is>
-      </c>
-      <c r="F852" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B853" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C853" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25698,23 +25738,31 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>-19.2091689</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E853" t="inlineStr">
         <is>
-          <t>-44.24819679999999</t>
-        </is>
-      </c>
-      <c r="F853" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>DC-9519595/2026</t>
-        </is>
-      </c>
-      <c r="B854" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C854" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25722,25 +25770,29 @@
       </c>
       <c r="D854" t="inlineStr">
         <is>
-          <t>-19.347297668442856</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E854" t="inlineStr">
         <is>
-          <t>-44.17816254149293</t>
-        </is>
-      </c>
-      <c r="F854" t="inlineStr"/>
+          <t>-46.687872082284</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>DO-009482014/2025-L1</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>9482014</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C855" t="inlineStr">
@@ -25750,29 +25802,29 @@
       </c>
       <c r="D855" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E855" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>DO-009482046/2025-L2</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>9482046</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C856" t="inlineStr">
@@ -25782,29 +25834,29 @@
       </c>
       <c r="D856" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E856" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F856" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>DO-009482017/2025-L3</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>9482017</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
@@ -25814,29 +25866,29 @@
       </c>
       <c r="D857" t="inlineStr">
         <is>
-          <t>-19.9275586</t>
+          <t>-17.21201508102213</t>
         </is>
       </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>-43.983052</t>
+          <t>-46.687872082284</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2301901 000001/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C858" t="inlineStr">
@@ -25844,23 +25896,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C859" t="inlineStr">
@@ -25868,23 +25928,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C860" t="inlineStr">
@@ -25892,23 +25960,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F860" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9507997/2026</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9507997</t>
         </is>
       </c>
       <c r="C861" t="inlineStr">
@@ -25916,21 +25992,33 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D861" t="inlineStr"/>
-      <c r="E861" t="inlineStr"/>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>-17.10715545158923</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
       <c r="F861" t="inlineStr">
         <is>
-          <t>2301617 000003/2025</t>
+          <t>1301606 000002/2026</t>
         </is>
       </c>
     </row>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>DM-007/2024-A</t>
-        </is>
-      </c>
-      <c r="B862" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C862" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -25938,71 +26026,95 @@
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>-21.1994491</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
         <is>
-          <t>-43.7852868</t>
-        </is>
-      </c>
-      <c r="F862" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B863" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Obra 3</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D863" t="inlineStr">
         <is>
-          <t>-21.27464910003665</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E863" t="inlineStr">
         <is>
-          <t>-42.91331545001727</t>
-        </is>
-      </c>
-      <c r="F863" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B864" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D864" t="inlineStr">
         <is>
-          <t>-21.23264738347681</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E864" t="inlineStr">
         <is>
-          <t>-43.43361939286979</t>
-        </is>
-      </c>
-      <c r="F864" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>DC-9515457/2026</t>
-        </is>
-      </c>
-      <c r="B865" t="inlineStr"/>
+          <t>DC-9507997/2026</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>9507997</t>
+        </is>
+      </c>
       <c r="C865" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26010,89 +26122,105 @@
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>-21.23528484003703</t>
+          <t>-17.10715545158923</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
         <is>
-          <t>-43.44604111152106</t>
-        </is>
-      </c>
-      <c r="F865" t="inlineStr"/>
+          <t>-46.62095644999281</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>1301606 000002/2026</t>
+        </is>
+      </c>
     </row>
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>DC-9519020/2026</t>
-        </is>
-      </c>
-      <c r="B866" t="inlineStr"/>
+          <t>DC-9501894/2026</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>9501894</t>
+        </is>
+      </c>
       <c r="C866" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D866" t="inlineStr">
-        <is>
-          <t>-19.6107675</t>
-        </is>
-      </c>
-      <c r="E866" t="inlineStr">
-        <is>
-          <t>-42.64891799999999</t>
-        </is>
-      </c>
+      <c r="D866" t="inlineStr"/>
+      <c r="E866" t="inlineStr"/>
       <c r="F866" t="inlineStr"/>
     </row>
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>DC-9518942/2026</t>
-        </is>
-      </c>
-      <c r="B867" t="inlineStr"/>
+          <t>DC-9518766/2026</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>9518766</t>
+        </is>
+      </c>
       <c r="C867" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>-15.483562</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>-44.39677500000001</t>
+        </is>
+      </c>
       <c r="F867" t="inlineStr"/>
     </row>
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9518766/2026</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9518766</t>
         </is>
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
-      <c r="F868" t="inlineStr">
-        <is>
-          <t>1301606 000002/2025</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>-15.5007309</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>-44.7624674</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr"/>
     </row>
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>DC-9496643/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>9496643</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C869" t="inlineStr">
@@ -26102,29 +26230,25 @@
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>-19.78548575576804</t>
+          <t>-19.2091689</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
         <is>
-          <t>-43.9495793253305</t>
-        </is>
-      </c>
-      <c r="F869" t="inlineStr">
-        <is>
-          <t>1301606 000002/2025</t>
-        </is>
-      </c>
+          <t>-44.24819679999999</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr"/>
     </row>
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>DC-9498666/2026</t>
+          <t>DC-9519595/2026</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>9453556</t>
+          <t>9519595</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
@@ -26132,23 +26256,27 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
-      <c r="F870" t="inlineStr">
-        <is>
-          <t>2301520 000041/2025</t>
-        </is>
-      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>-19.347297668442856</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>-44.17816254149293</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr"/>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>DM-008/2024-A</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>9422064</t>
+          <t>9482014</t>
         </is>
       </c>
       <c r="C871" t="inlineStr">
@@ -26156,23 +26284,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>DM-011/2024-A</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>9421657</t>
+          <t>9482046</t>
         </is>
       </c>
       <c r="C872" t="inlineStr">
@@ -26182,29 +26318,29 @@
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>-17.335013</t>
+          <t>-19.9275586</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>-44.943418</t>
+          <t>-43.983052</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>DM-009/2024-A</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>9422078</t>
+          <t>9482017</t>
         </is>
       </c>
       <c r="C873" t="inlineStr">
@@ -26212,23 +26348,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
       <c r="F873" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301901 000001/2025</t>
         </is>
       </c>
     </row>
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>DM-010/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>9418600</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C874" t="inlineStr">
@@ -26240,17 +26384,21 @@
       <c r="E874" t="inlineStr"/>
       <c r="F874" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AMA-9502187/2026</t>
-        </is>
-      </c>
-      <c r="B875" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C875" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26258,15 +26406,23 @@
       </c>
       <c r="D875" t="inlineStr"/>
       <c r="E875" t="inlineStr"/>
-      <c r="F875" t="inlineStr"/>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>DM-9500304/2026</t>
-        </is>
-      </c>
-      <c r="B876" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C876" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26274,41 +26430,45 @@
       </c>
       <c r="D876" t="inlineStr"/>
       <c r="E876" t="inlineStr"/>
-      <c r="F876" t="inlineStr"/>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DM-9512043/2026</t>
-        </is>
-      </c>
-      <c r="B877" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C877" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D877" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E877" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
-      <c r="F877" t="inlineStr"/>
+      <c r="D877" t="inlineStr"/>
+      <c r="E877" t="inlineStr"/>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DC-9497471/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>9497471</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C878" t="inlineStr">
@@ -26316,125 +26476,121 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D878" t="inlineStr">
-        <is>
-          <t>-19.747173</t>
-        </is>
-      </c>
-      <c r="E878" t="inlineStr">
-        <is>
-          <t>-50.219328</t>
-        </is>
-      </c>
+      <c r="D878" t="inlineStr"/>
+      <c r="E878" t="inlineStr"/>
       <c r="F878" t="inlineStr">
         <is>
-          <t>1301606 000003/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
-        </is>
-      </c>
-      <c r="B879" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C879" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D879" t="inlineStr">
-        <is>
-          <t>-19.0966327</t>
-        </is>
-      </c>
-      <c r="E879" t="inlineStr">
-        <is>
-          <t>-46.67356590000001</t>
-        </is>
-      </c>
-      <c r="F879" t="inlineStr"/>
+      <c r="D879" t="inlineStr"/>
+      <c r="E879" t="inlineStr"/>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>DC-9519295/2026</t>
-        </is>
-      </c>
-      <c r="B880" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C880" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D880" t="inlineStr">
-        <is>
-          <t>-19.071165</t>
-        </is>
-      </c>
-      <c r="E880" t="inlineStr">
-        <is>
-          <t>-46.794155</t>
-        </is>
-      </c>
-      <c r="F880" t="inlineStr"/>
+      <c r="D880" t="inlineStr"/>
+      <c r="E880" t="inlineStr"/>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
-      <c r="B881" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C881" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D881" t="inlineStr">
-        <is>
-          <t>-20.011794067707264</t>
-        </is>
-      </c>
-      <c r="E881" t="inlineStr">
-        <is>
-          <t>-44.21840097426832</t>
-        </is>
-      </c>
-      <c r="F881" t="inlineStr"/>
+      <c r="D881" t="inlineStr"/>
+      <c r="E881" t="inlineStr"/>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>DC-9518140/2026</t>
-        </is>
-      </c>
-      <c r="B882" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C882" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D882" t="inlineStr">
-        <is>
-          <t>-20.051632324197044</t>
-        </is>
-      </c>
-      <c r="E882" t="inlineStr">
-        <is>
-          <t>-44.19399735422576</t>
-        </is>
-      </c>
-      <c r="F882" t="inlineStr"/>
+      <c r="D882" t="inlineStr"/>
+      <c r="E882" t="inlineStr"/>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>DM-9512044/2026</t>
-        </is>
-      </c>
-      <c r="B883" t="inlineStr"/>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
       <c r="C883" t="inlineStr">
         <is>
           <t>Obra 1</t>
@@ -26442,49 +26598,45 @@
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr"/>
-      <c r="F883" t="inlineStr"/>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>DO-001/2021- C</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>9275590</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D884" t="inlineStr">
-        <is>
-          <t>-19.928208</t>
-        </is>
-      </c>
-      <c r="E884" t="inlineStr">
-        <is>
-          <t>-43.983328</t>
-        </is>
-      </c>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr"/>
+      <c r="E884" t="inlineStr"/>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2301901 000003/2021</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>DM-017/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>9424449</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C885" t="inlineStr">
@@ -26496,19 +26648,19 @@
       <c r="E885" t="inlineStr"/>
       <c r="F885" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>DM-014/2024-A</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>9424302</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C886" t="inlineStr">
@@ -26516,31 +26668,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D886" t="inlineStr">
-        <is>
-          <t>-19.8618029</t>
-        </is>
-      </c>
-      <c r="E886" t="inlineStr">
-        <is>
-          <t>-44.5829004</t>
-        </is>
-      </c>
+      <c r="D886" t="inlineStr"/>
+      <c r="E886" t="inlineStr"/>
       <c r="F886" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>PRC-29.008/2017-E</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>9149606</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C887" t="inlineStr">
@@ -26548,31 +26692,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D887" t="inlineStr">
-        <is>
-          <t>-16.7203311</t>
-        </is>
-      </c>
-      <c r="E887" t="inlineStr">
-        <is>
-          <t>-43.8541147</t>
-        </is>
-      </c>
+      <c r="D887" t="inlineStr"/>
+      <c r="E887" t="inlineStr"/>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2301901 000001/2017</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>DC-9505062/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>9505062</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C888" t="inlineStr">
@@ -26580,31 +26716,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D888" t="inlineStr">
-        <is>
-          <t>-22.6434039</t>
-        </is>
-      </c>
-      <c r="E888" t="inlineStr">
-        <is>
-          <t>-46.3795013</t>
-        </is>
-      </c>
+      <c r="D888" t="inlineStr"/>
+      <c r="E888" t="inlineStr"/>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2301520 000044/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>DM-9504058/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>9504058</t>
+          <t>9499286</t>
         </is>
       </c>
       <c r="C889" t="inlineStr">
@@ -26612,31 +26740,23 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D889" t="inlineStr">
-        <is>
-          <t>-19.9275586</t>
-        </is>
-      </c>
-      <c r="E889" t="inlineStr">
-        <is>
-          <t>-43.983052</t>
-        </is>
-      </c>
+      <c r="D889" t="inlineStr"/>
+      <c r="E889" t="inlineStr"/>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2301762 000030/2025</t>
+          <t>2301617 000003/2025</t>
         </is>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-007/2024-A</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9422060</t>
         </is>
       </c>
       <c r="C890" t="inlineStr">
@@ -26644,71 +26764,83 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D890" t="inlineStr"/>
-      <c r="E890" t="inlineStr"/>
-      <c r="F890" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>-21.1994491</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>-43.7852868</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr"/>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D891" t="inlineStr"/>
-      <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>-21.27464910003665</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>-42.91331545001727</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr"/>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D892" t="inlineStr"/>
-      <c r="E892" t="inlineStr"/>
-      <c r="F892" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>-21.23264738347681</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>-43.43361939286979</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr"/>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DC-9515457/2026</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>9499286</t>
+          <t>9515457</t>
         </is>
       </c>
       <c r="C893" t="inlineStr">
@@ -26716,55 +26848,55 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D893" t="inlineStr"/>
-      <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr">
-        <is>
-          <t>2301617 000003/2025</t>
-        </is>
-      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>-21.23528484003703</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>-43.44604111152106</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr"/>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9519020/2026</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9519020</t>
         </is>
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Obra 2</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
         <is>
-          <t>-16.11741660736296</t>
+          <t>-19.6107675</t>
         </is>
       </c>
       <c r="E894" t="inlineStr">
         <is>
-          <t>-45.71048533230583</t>
-        </is>
-      </c>
-      <c r="F894" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+          <t>-42.64891799999999</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr"/>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9518942/2026</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9518942</t>
         </is>
       </c>
       <c r="C895" t="inlineStr">
@@ -26772,63 +26904,43 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D895" t="inlineStr">
-        <is>
-          <t>-16.11921421383736</t>
-        </is>
-      </c>
-      <c r="E895" t="inlineStr">
-        <is>
-          <t>-45.58712745575681</t>
-        </is>
-      </c>
-      <c r="F895" t="inlineStr">
-        <is>
-          <t>2301520 000037/2025</t>
-        </is>
-      </c>
+      <c r="D895" t="inlineStr"/>
+      <c r="E895" t="inlineStr"/>
+      <c r="F895" t="inlineStr"/>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>9501601</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D896" t="inlineStr">
-        <is>
-          <t>-16.12119845072</t>
-        </is>
-      </c>
-      <c r="E896" t="inlineStr">
-        <is>
-          <t>-45.6488268407393</t>
-        </is>
-      </c>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr"/>
+      <c r="E896" t="inlineStr"/>
       <c r="F896" t="inlineStr">
         <is>
-          <t>2301520 000037/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>DC-9493529/2026</t>
+          <t>DC-9496643/2026</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>9493529</t>
+          <t>9496643</t>
         </is>
       </c>
       <c r="C897" t="inlineStr">
@@ -26836,23 +26948,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D897" t="inlineStr"/>
-      <c r="E897" t="inlineStr"/>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>-19.78548575576804</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>-43.9495793253305</t>
+        </is>
+      </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>2301520 000036/2025</t>
+          <t>1301606 000002/2025</t>
         </is>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>DM-012/2024-A</t>
+          <t>DC-9498666/2026</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>9422079</t>
+          <t>9453556</t>
         </is>
       </c>
       <c r="C898" t="inlineStr">
@@ -26864,19 +26984,19 @@
       <c r="E898" t="inlineStr"/>
       <c r="F898" t="inlineStr">
         <is>
-          <t>2301762 000036/2023</t>
+          <t>2301520 000041/2025</t>
         </is>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>DM-9502116/2026</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>9502116</t>
+          <t>9422064</t>
         </is>
       </c>
       <c r="C899" t="inlineStr">
@@ -26888,19 +27008,19 @@
       <c r="E899" t="inlineStr"/>
       <c r="F899" t="inlineStr">
         <is>
-          <t>2301762 000026/2025</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>DM-018/2024-A</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>9424304</t>
+          <t>9421657</t>
         </is>
       </c>
       <c r="C900" t="inlineStr">
@@ -26908,23 +27028,31 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D900" t="inlineStr"/>
-      <c r="E900" t="inlineStr"/>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>-17.335013</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>-44.943418</t>
+        </is>
+      </c>
       <c r="F900" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>DM-016/2024-A</t>
+          <t>DM-009/2024-A</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>9424337</t>
+          <t>9422078</t>
         </is>
       </c>
       <c r="C901" t="inlineStr">
@@ -26936,19 +27064,19 @@
       <c r="E901" t="inlineStr"/>
       <c r="F901" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>DM-020/2024-A</t>
+          <t>DM-010/2024-A</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>9427674</t>
+          <t>9418600</t>
         </is>
       </c>
       <c r="C902" t="inlineStr">
@@ -26956,64 +27084,44 @@
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D902" t="inlineStr">
-        <is>
-          <t>-17.8518635</t>
-        </is>
-      </c>
-      <c r="E902" t="inlineStr">
-        <is>
-          <t>-41.5076927</t>
-        </is>
-      </c>
+      <c r="D902" t="inlineStr"/>
+      <c r="E902" t="inlineStr"/>
       <c r="F902" t="inlineStr">
         <is>
-          <t>2301762 000051/2023</t>
+          <t>2301762 000036/2023</t>
         </is>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>DM-022/2024-A</t>
-        </is>
-      </c>
-      <c r="B903" t="inlineStr">
-        <is>
-          <t>9427765</t>
-        </is>
-      </c>
+          <t xml:space="preserve">  AMA-9502187/2026</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr"/>
       <c r="C903" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D903" t="inlineStr">
-        <is>
-          <t>-20.6829764</t>
-        </is>
-      </c>
-      <c r="E903" t="inlineStr">
-        <is>
-          <t>-44.8232506</t>
-        </is>
-      </c>
-      <c r="F903" t="inlineStr">
-        <is>
-          <t>2301762 000051/2023</t>
-        </is>
-      </c>
+      <c r="D903" t="inlineStr"/>
+      <c r="E903" t="inlineStr"/>
+      <c r="F903" t="inlineStr"/>
     </row>
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B904" t="inlineStr"/>
+          <t>DM-9500304/2026</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>9500304</t>
+        </is>
+      </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Obra 4</t>
+          <t>Obra 1</t>
         </is>
       </c>
       <c r="D904" t="inlineStr"/>
@@ -27023,90 +27131,1170 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B905" t="inlineStr"/>
+          <t>DM-9512043/2026</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>9512043</t>
+        </is>
+      </c>
       <c r="C905" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D905" t="inlineStr"/>
-      <c r="E905" t="inlineStr"/>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
       <c r="F905" t="inlineStr"/>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B906" t="inlineStr"/>
+          <t>DC-9497471/2026</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>9497471</t>
+        </is>
+      </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>Obra 3</t>
-        </is>
-      </c>
-      <c r="D906" t="inlineStr"/>
-      <c r="E906" t="inlineStr"/>
-      <c r="F906" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>-19.747173</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>-50.219328</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>1301606 000003/2025</t>
+        </is>
+      </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>DC-9511902/2026</t>
-        </is>
-      </c>
-      <c r="B907" t="inlineStr"/>
+          <t>DC-9519295/2026</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>Obra 2</t>
-        </is>
-      </c>
-      <c r="D907" t="inlineStr"/>
-      <c r="E907" t="inlineStr"/>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>-19.0966327</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>-46.67356590000001</t>
+        </is>
+      </c>
       <c r="F907" t="inlineStr"/>
     </row>
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>DM-9519034/2026</t>
-        </is>
-      </c>
-      <c r="B908" t="inlineStr"/>
+          <t>DC-9519295/2026</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>9519295</t>
+        </is>
+      </c>
       <c r="C908" t="inlineStr">
         <is>
           <t>Obra 1</t>
         </is>
       </c>
-      <c r="D908" t="inlineStr"/>
-      <c r="E908" t="inlineStr"/>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>-19.071165</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>-46.794155</t>
+        </is>
+      </c>
       <c r="F908" t="inlineStr"/>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>-20.011794067707264</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>-44.21840097426832</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>DC-9518140/2026</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>9518140</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>-20.051632324197044</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>-44.19399735422576</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>DM-9512044/2026</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>9512044</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr"/>
+      <c r="E911" t="inlineStr"/>
+      <c r="F911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>9275590</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>-19.928208</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>-43.983328</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>2301901 000003/2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>DM-017/2024-A</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>9424449</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr"/>
+      <c r="E913" t="inlineStr"/>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>DM-014/2024-A</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>9424302</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>-19.8618029</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>-44.5829004</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>PRC-29.008/2017-E</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>9149606</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>-16.7203311</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>-43.8541147</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>2301901 000001/2017</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>DC-9505062/2026</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>9505062</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>-22.6434039</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>-46.3795013</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>2301520 000044/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>DM-9504058/2026</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>9504058</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>-19.9275586</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>-43.983052</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>2301762 000030/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr"/>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr"/>
+      <c r="E921" t="inlineStr"/>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="inlineStr"/>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr"/>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr"/>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr"/>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr"/>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr"/>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr"/>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr"/>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr"/>
+      <c r="E932" t="inlineStr"/>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>9499286</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr"/>
+      <c r="E933" t="inlineStr"/>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>2301617 000003/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>-16.11741660736296</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>-45.71048533230583</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>-16.11921421383736</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>-45.58712745575681</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>9501601</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>-16.12119845072</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>-45.6488268407393</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>2301520 000037/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>DC-9493529/2026</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>9493529</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr"/>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>2301520 000036/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>9422079</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr"/>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>2301762 000036/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>9502116</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr"/>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>2301762 000026/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>9424304</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>9424337</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr"/>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>DM-020/2024-A</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>9427674</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>-17.8518635</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>-41.5076927</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>DM-022/2024-A</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>9427765</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>-20.6829764</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>-44.8232506</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>2301762 000051/2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Obra 4</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr"/>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr"/>
+      <c r="E945" t="inlineStr"/>
+      <c r="F945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Obra 3</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr"/>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>DC-9511902/2026</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>9511902</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Obra 2</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr"/>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>DM-9519034/2026</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>9519034</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr"/>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
           <t>DC-9519017/2026</t>
         </is>
       </c>
-      <c r="B909" t="inlineStr"/>
-      <c r="C909" t="inlineStr">
-        <is>
-          <t>Obra 1</t>
-        </is>
-      </c>
-      <c r="D909" t="inlineStr">
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>9519017</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Obra 1</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
         <is>
           <t>-18.46005275010656</t>
         </is>
       </c>
-      <c r="E909" t="inlineStr">
+      <c r="E949" t="inlineStr">
         <is>
           <t>-48.18218127247928</t>
         </is>
       </c>
-      <c r="F909" t="inlineStr"/>
+      <c r="F949" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
